--- a/data-raw/gtsummary_translated.xlsx
+++ b/data-raw/gtsummary_translated.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dzana\GitHub\gtsummary\data-raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sjobergd/Documents/GitHub/gtsummary/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476F6E89-2A57-4610-A764-DF18B27207C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7BC3EB0-4D26-CA43-B0CD-29E421BECF0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{24D5C74B-D2E9-42BC-9756-BFD64AB81539}"/>
+    <workbookView xWindow="10180" yWindow="22360" windowWidth="30240" windowHeight="18880" xr2:uid="{24D5C74B-D2E9-42BC-9756-BFD64AB81539}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="1055">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="1062">
   <si>
     <t>context</t>
   </si>
@@ -137,9 +137,6 @@
     <t>p-Wert</t>
   </si>
   <si>
-    <t>p-valeur</t>
-  </si>
-  <si>
     <t>One-way ANOVA</t>
   </si>
   <si>
@@ -188,9 +185,6 @@
     <t>T-Test</t>
   </si>
   <si>
-    <t>test de Student</t>
-  </si>
-  <si>
     <t>tbl_regression</t>
   </si>
   <si>
@@ -443,9 +437,6 @@
     <t>Hommel-Korrektur für multiples Testen</t>
   </si>
   <si>
-    <t xml:space="preserve">Correctionde Hommel pour tests multiples </t>
-  </si>
-  <si>
     <t>Correção de Hommel para testes múltiplos</t>
   </si>
   <si>
@@ -531,9 +522,6 @@
   </si>
   <si>
     <t>q-Wert</t>
-  </si>
-  <si>
-    <t>q-valeur</t>
   </si>
   <si>
     <t>add_overall</t>
@@ -2298,9 +2286,6 @@
     <t>log-vraisemblance</t>
   </si>
   <si>
-    <t>degrés de liberté des résidus</t>
-  </si>
-  <si>
     <t>déviance nulle</t>
   </si>
   <si>
@@ -2349,12 +2334,6 @@
     <t>test d'indépendance de Wald ajusté pour les plans d'échantillonnage complexes</t>
   </si>
   <si>
-    <t>test du Chi² ajusté selon une estimation de l'effet du plan d'échantillonnage</t>
-  </si>
-  <si>
-    <t>test du Chi² avec la correction du second ordre de Rao &amp; Scott</t>
-  </si>
-  <si>
     <t>test de Kruskal-Wallis avec prise en compte du plan d'échantillonnage</t>
   </si>
   <si>
@@ -2853,45 +2832,9 @@
     <t xml:space="preserve">Marginal Predictions </t>
   </si>
   <si>
-    <t xml:space="preserve"> Effets Marginaux Moyens</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Effets Marginaux à la Moyenne</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Effets Marginaux aux Moyennes Marginales</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Effets Marginaux</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Contrastes Marginaux Moyens</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Contrastes Marginaux à la Moyenne</t>
   </si>
   <si>
-    <t xml:space="preserve"> Contrastes Marginaux aux Moyennes Marginales</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Contrastes Marginaux</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Moyennes Marginales</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Prédictions Marginales Moyennes</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Prédictions Marginales à la Moyenne</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Prédictions Marginales aux Moyennes Marginales</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Prédictions Marginales</t>
-  </si>
-  <si>
     <t>{style_sigfig(prob, scale=100)}% Percentile</t>
   </si>
   <si>
@@ -3304,6 +3247,84 @@
   </si>
   <si>
     <t>Devijanca za nul-model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Degrés de liberté résiduels</t>
+  </si>
+  <si>
+    <t>Valeur p</t>
+  </si>
+  <si>
+    <t>Test t de Welch</t>
+  </si>
+  <si>
+    <t>Test de Student</t>
+  </si>
+  <si>
+    <t>Test de Student apparié</t>
+  </si>
+  <si>
+    <t>Test de McNemar avec correction de continuité</t>
+  </si>
+  <si>
+    <t>Test de McNemar</t>
+  </si>
+  <si>
+    <t>Correction de Hommel pour tests multiples</t>
+  </si>
+  <si>
+    <t>Valeur q</t>
+  </si>
+  <si>
+    <t>IC = intervalle de crédibilité</t>
+  </si>
+  <si>
+    <t>Intervalle de crédibilité</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Effets marginaux moyens</t>
+  </si>
+  <si>
+    <t>Effets marginaux à la moyenne</t>
+  </si>
+  <si>
+    <t>Effets marginaux aux moyennes marginales</t>
+  </si>
+  <si>
+    <t>Effets marginaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Contrastes marginaux moyens</t>
+  </si>
+  <si>
+    <t>Contrastes marginaux à la moyenne</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Contrastes marginaux aux moyennes marginales</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Contrastes marginaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Moyennes marginales</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Prédictions marginales moyennes</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Prédictions marginales à la moyenne</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Prédictions marginales</t>
+  </si>
+  <si>
+    <t>à</t>
+  </si>
+  <si>
+    <t>test du khi-deux ajusté selon une estimation de l'effet du plan d'échantillonnage</t>
+  </si>
+  <si>
+    <t>test du khi-deux avec la correction du second ordre de Rao &amp; Scott</t>
   </si>
 </sst>
 </file>
@@ -3409,7 +3430,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3434,7 +3455,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3750,29 +3770,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2D53F92-7994-419F-B91C-749F7CB570B6}">
   <dimension ref="A1:R111"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.796875" customWidth="1"/>
+    <col min="1" max="1" width="23.83203125" customWidth="1"/>
     <col min="2" max="2" width="80" customWidth="1"/>
     <col min="3" max="3" width="49" style="9" customWidth="1"/>
     <col min="4" max="4" width="47.33203125" customWidth="1"/>
-    <col min="5" max="5" width="53.46484375" style="9" customWidth="1"/>
-    <col min="6" max="6" width="38.46484375" customWidth="1"/>
-    <col min="7" max="7" width="15.1328125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="39.46484375" customWidth="1"/>
+    <col min="5" max="5" width="53.5" style="9" customWidth="1"/>
+    <col min="6" max="6" width="38.5" customWidth="1"/>
+    <col min="7" max="7" width="15.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="39.5" customWidth="1"/>
     <col min="9" max="9" width="49" customWidth="1"/>
     <col min="10" max="10" width="67" customWidth="1"/>
     <col min="11" max="11" width="51" customWidth="1"/>
     <col min="12" max="12" width="52" customWidth="1"/>
     <col min="13" max="13" width="52.6640625" customWidth="1"/>
-    <col min="14" max="14" width="57.46484375" customWidth="1"/>
-    <col min="15" max="15" width="58.46484375" customWidth="1"/>
+    <col min="14" max="14" width="57.5" customWidth="1"/>
+    <col min="15" max="15" width="58.5" customWidth="1"/>
     <col min="16" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="19.9296875" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="20" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="33.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" ht="16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3780,25 +3800,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="D1" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="F1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="G1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="H1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="I1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="J1" t="s">
         <v>2</v>
@@ -3813,245 +3833,245 @@
         <v>5</v>
       </c>
       <c r="N1" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="O1" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="P1" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="Q1" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="R1" t="s">
-        <v>967</v>
+        <v>948</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B2" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="R2" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B3" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="L3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="O3" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="Q3" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="R3" t="s">
-        <v>1027</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B4" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="L4" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="Q4" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="R4" t="s">
-        <v>1028</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B5" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L5" t="s">
-        <v>719</v>
+        <v>1036</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="Q5" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="R5" t="s">
-        <v>1029</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B6" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="L6" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="Q6" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="R6" t="s">
-        <v>1054</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" t="s">
+        <v>590</v>
+      </c>
+      <c r="B7" t="s">
         <v>594</v>
       </c>
-      <c r="B7" t="s">
-        <v>598</v>
-      </c>
       <c r="L7" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="Q7" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="R7" t="s">
-        <v>1053</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B8" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="L8" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="R8" t="s">
-        <v>1030</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B9" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="R9" t="s">
-        <v>1031</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B10" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="L10" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="R10" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="16">
       <c r="A11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B11" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="F11" t="s">
+        <v>285</v>
+      </c>
+      <c r="G11" t="s">
+        <v>285</v>
+      </c>
+      <c r="H11" t="s">
+        <v>243</v>
+      </c>
+      <c r="J11" t="s">
+        <v>162</v>
+      </c>
+      <c r="K11" t="s">
+        <v>163</v>
+      </c>
+      <c r="L11" t="s">
         <v>164</v>
       </c>
-      <c r="B11" t="s">
-        <v>165</v>
-      </c>
-      <c r="C11" s="9" t="s">
+      <c r="M11" t="s">
+        <v>164</v>
+      </c>
+      <c r="N11" t="s">
+        <v>613</v>
+      </c>
+      <c r="P11" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>821</v>
+      </c>
+      <c r="R11" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="16">
+      <c r="A12" t="s">
+        <v>607</v>
+      </c>
+      <c r="B12" t="s">
+        <v>606</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>384</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="F11" t="s">
-        <v>289</v>
-      </c>
-      <c r="G11" t="s">
-        <v>289</v>
-      </c>
-      <c r="H11" t="s">
-        <v>247</v>
-      </c>
-      <c r="J11" t="s">
-        <v>166</v>
-      </c>
-      <c r="K11" t="s">
-        <v>167</v>
-      </c>
-      <c r="L11" t="s">
-        <v>168</v>
-      </c>
-      <c r="M11" t="s">
-        <v>168</v>
-      </c>
-      <c r="N11" t="s">
-        <v>617</v>
-      </c>
-      <c r="P11" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>828</v>
-      </c>
-      <c r="R11" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12" t="s">
-        <v>611</v>
-      </c>
-      <c r="B12" t="s">
-        <v>610</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>388</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G12" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="H12" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="I12" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="J12" t="s">
         <v>14</v>
@@ -4066,48 +4086,48 @@
         <v>17</v>
       </c>
       <c r="N12" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="P12" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="Q12" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
       <c r="R12" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="16">
       <c r="A13" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B13" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="F13" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="G13" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="H13" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="I13" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J13" t="s">
         <v>19</v>
@@ -4122,154 +4142,154 @@
         <v>22</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="P13" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="Q13" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
       <c r="R13" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="16">
       <c r="A14" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B14" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C14" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G14" t="s">
+        <v>288</v>
+      </c>
+      <c r="H14" t="s">
+        <v>244</v>
+      </c>
+      <c r="I14" t="s">
+        <v>35</v>
+      </c>
+      <c r="J14" t="s">
+        <v>36</v>
+      </c>
+      <c r="K14" t="s">
+        <v>37</v>
+      </c>
+      <c r="L14" t="s">
+        <v>38</v>
+      </c>
+      <c r="M14" t="s">
+        <v>39</v>
+      </c>
+      <c r="O14" s="11" t="s">
+        <v>659</v>
+      </c>
+      <c r="P14" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>824</v>
+      </c>
+      <c r="R14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="16">
+      <c r="A15" t="s">
+        <v>607</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>392</v>
       </c>
-      <c r="D14" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="G14" t="s">
-        <v>292</v>
-      </c>
-      <c r="H14" t="s">
-        <v>248</v>
-      </c>
-      <c r="I14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J14" t="s">
-        <v>37</v>
-      </c>
-      <c r="K14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L14" t="s">
-        <v>39</v>
-      </c>
-      <c r="M14" t="s">
-        <v>40</v>
-      </c>
-      <c r="O14" s="11" t="s">
-        <v>663</v>
-      </c>
-      <c r="P14" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>831</v>
-      </c>
-      <c r="R14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" t="s">
-        <v>611</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="F15" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="G15" t="s">
+        <v>289</v>
+      </c>
+      <c r="H15" t="s">
+        <v>220</v>
+      </c>
+      <c r="I15" t="s">
+        <v>190</v>
+      </c>
+      <c r="J15" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="G15" t="s">
-        <v>293</v>
-      </c>
-      <c r="H15" t="s">
-        <v>224</v>
-      </c>
-      <c r="I15" t="s">
-        <v>194</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>33</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
         <v>34</v>
       </c>
-      <c r="L15" t="s">
-        <v>35</v>
-      </c>
       <c r="M15" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="N15" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="O15" s="12" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="P15" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="Q15" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="R15" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="16">
       <c r="A16" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B16" t="s">
         <v>28</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="G16" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="H16" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="I16" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="J16" t="s">
         <v>29</v>
@@ -4278,104 +4298,104 @@
         <v>30</v>
       </c>
       <c r="L16" t="s">
-        <v>31</v>
+        <v>1037</v>
       </c>
       <c r="M16" t="s">
-        <v>937</v>
+        <v>918</v>
       </c>
       <c r="N16" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="O16" s="12" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="P16" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="Q16" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="R16" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="16">
       <c r="A17" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="G17" t="s">
+        <v>291</v>
+      </c>
+      <c r="H17" t="s">
+        <v>246</v>
+      </c>
+      <c r="I17" t="s">
+        <v>192</v>
+      </c>
+      <c r="J17" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>400</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>402</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="G17" t="s">
-        <v>295</v>
-      </c>
-      <c r="H17" t="s">
-        <v>250</v>
-      </c>
-      <c r="I17" t="s">
-        <v>196</v>
-      </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>42</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" t="s">
         <v>43</v>
       </c>
-      <c r="L17" t="s">
-        <v>44</v>
-      </c>
       <c r="M17" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="P17" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="Q17" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="R17" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="16">
       <c r="A18" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="F18" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G18" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="H18" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="I18" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="J18" t="s">
         <v>24</v>
@@ -4390,48 +4410,48 @@
         <v>27</v>
       </c>
       <c r="N18" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="O18" s="12" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="P18" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="Q18" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="R18" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="16">
       <c r="A19" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B19" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="G19" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="H19" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I19" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="J19" t="s">
         <v>7</v>
@@ -4446,131 +4466,134 @@
         <v>10</v>
       </c>
       <c r="N19" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="O19" s="12" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="P19" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="Q19" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="R19" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="16">
       <c r="A20" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B20" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G20" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="H20" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="I20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J20" t="s">
         <v>45</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>46</v>
       </c>
-      <c r="K20" t="s">
-        <v>47</v>
-      </c>
       <c r="L20" t="s">
-        <v>48</v>
+        <v>1038</v>
       </c>
       <c r="M20" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="N20" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="O20" s="11" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="P20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q20" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="R20" t="s">
-        <v>976</v>
+        <v>957</v>
       </c>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B21" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="D21" s="9"/>
       <c r="F21" s="3"/>
       <c r="G21"/>
+      <c r="L21" t="s">
+        <v>1039</v>
+      </c>
       <c r="M21" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="O21" s="11"/>
       <c r="P21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q21" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="R21" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="16">
       <c r="A22" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B22" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="G22" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="H22" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="I22" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="J22" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="K22" t="s">
         <v>11</v>
@@ -4582,3371 +4605,3389 @@
         <v>13</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="P22" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="Q22" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
       <c r="R22" t="s">
-        <v>978</v>
+        <v>959</v>
       </c>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B23" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="D23" s="9"/>
       <c r="F23" s="6"/>
       <c r="G23"/>
+      <c r="L23" t="s">
+        <v>1040</v>
+      </c>
       <c r="M23" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="O23" s="11"/>
       <c r="P23" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="Q23" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="R23" t="s">
-        <v>979</v>
+        <v>960</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B24" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="D24" s="9"/>
       <c r="F24" s="6"/>
       <c r="G24"/>
+      <c r="L24" t="s">
+        <v>1041</v>
+      </c>
       <c r="M24" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="O24" s="11"/>
       <c r="P24" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="Q24" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="R24" t="s">
-        <v>980</v>
+        <v>961</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="A25" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B25" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="D25" s="9"/>
       <c r="F25" s="6"/>
       <c r="G25"/>
+      <c r="L25" t="s">
+        <v>1042</v>
+      </c>
       <c r="M25" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="O25" s="11"/>
       <c r="P25" t="s">
+        <v>775</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>834</v>
+      </c>
+      <c r="R25" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="16">
+      <c r="A26" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="F26" t="s">
+        <v>343</v>
+      </c>
+      <c r="G26" t="s">
+        <v>296</v>
+      </c>
+      <c r="H26" t="s">
+        <v>249</v>
+      </c>
+      <c r="I26" t="s">
+        <v>196</v>
+      </c>
+      <c r="J26" t="s">
+        <v>138</v>
+      </c>
+      <c r="K26" t="s">
+        <v>139</v>
+      </c>
+      <c r="L26" t="s">
+        <v>140</v>
+      </c>
+      <c r="M26" t="s">
+        <v>141</v>
+      </c>
+      <c r="O26" s="12" t="s">
+        <v>664</v>
+      </c>
+      <c r="P26" t="s">
+        <v>776</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>835</v>
+      </c>
+      <c r="R26" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="16">
+      <c r="A27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" t="s">
+        <v>142</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="D27" t="s">
+        <v>415</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="F27" t="s">
+        <v>344</v>
+      </c>
+      <c r="G27" t="s">
+        <v>297</v>
+      </c>
+      <c r="H27" t="s">
+        <v>250</v>
+      </c>
+      <c r="I27" t="s">
+        <v>197</v>
+      </c>
+      <c r="J27" t="s">
+        <v>143</v>
+      </c>
+      <c r="K27" t="s">
+        <v>144</v>
+      </c>
+      <c r="L27" t="s">
+        <v>145</v>
+      </c>
+      <c r="M27" t="s">
+        <v>146</v>
+      </c>
+      <c r="O27" s="12" t="s">
+        <v>665</v>
+      </c>
+      <c r="P27" t="s">
+        <v>777</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>836</v>
+      </c>
+      <c r="R27" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="16">
+      <c r="A28" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="D28" t="s">
+        <v>418</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="F28" t="s">
+        <v>345</v>
+      </c>
+      <c r="G28" t="s">
+        <v>298</v>
+      </c>
+      <c r="H28" t="s">
+        <v>251</v>
+      </c>
+      <c r="I28" t="s">
+        <v>198</v>
+      </c>
+      <c r="J28" t="s">
+        <v>133</v>
+      </c>
+      <c r="K28" t="s">
+        <v>134</v>
+      </c>
+      <c r="L28" t="s">
+        <v>135</v>
+      </c>
+      <c r="M28" t="s">
+        <v>136</v>
+      </c>
+      <c r="O28" s="12" t="s">
+        <v>666</v>
+      </c>
+      <c r="P28" t="s">
+        <v>778</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>837</v>
+      </c>
+      <c r="R28" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="16">
+      <c r="A29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B29" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="D29" t="s">
+        <v>421</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="F29" t="s">
+        <v>346</v>
+      </c>
+      <c r="G29" t="s">
+        <v>299</v>
+      </c>
+      <c r="H29" t="s">
+        <v>252</v>
+      </c>
+      <c r="I29" t="s">
+        <v>199</v>
+      </c>
+      <c r="J29" t="s">
+        <v>148</v>
+      </c>
+      <c r="K29" t="s">
+        <v>149</v>
+      </c>
+      <c r="L29" t="s">
+        <v>150</v>
+      </c>
+      <c r="M29" t="s">
+        <v>151</v>
+      </c>
+      <c r="O29" s="12" t="s">
+        <v>667</v>
+      </c>
+      <c r="P29" t="s">
+        <v>779</v>
+      </c>
+      <c r="Q29" s="13" t="s">
+        <v>838</v>
+      </c>
+      <c r="R29" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="16">
+      <c r="A30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="D30" t="s">
+        <v>424</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="F30" t="s">
+        <v>347</v>
+      </c>
+      <c r="G30" t="s">
+        <v>300</v>
+      </c>
+      <c r="H30" t="s">
+        <v>253</v>
+      </c>
+      <c r="I30" t="s">
+        <v>200</v>
+      </c>
+      <c r="J30" t="s">
+        <v>124</v>
+      </c>
+      <c r="K30" t="s">
+        <v>125</v>
+      </c>
+      <c r="L30" t="s">
+        <v>126</v>
+      </c>
+      <c r="M30" t="s">
+        <v>127</v>
+      </c>
+      <c r="O30" s="12" t="s">
+        <v>668</v>
+      </c>
+      <c r="P30" t="s">
+        <v>780</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>839</v>
+      </c>
+      <c r="R30" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="16">
+      <c r="A31" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="D31" t="s">
+        <v>427</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="F31" t="s">
+        <v>348</v>
+      </c>
+      <c r="G31" t="s">
+        <v>301</v>
+      </c>
+      <c r="H31" t="s">
+        <v>254</v>
+      </c>
+      <c r="I31" t="s">
+        <v>201</v>
+      </c>
+      <c r="J31" t="s">
+        <v>119</v>
+      </c>
+      <c r="K31" t="s">
+        <v>120</v>
+      </c>
+      <c r="L31" t="s">
+        <v>121</v>
+      </c>
+      <c r="M31" t="s">
+        <v>122</v>
+      </c>
+      <c r="O31" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="P31" t="s">
+        <v>781</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>840</v>
+      </c>
+      <c r="R31" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="16">
+      <c r="A32" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="D32" t="s">
+        <v>430</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="F32" t="s">
+        <v>349</v>
+      </c>
+      <c r="G32" t="s">
+        <v>302</v>
+      </c>
+      <c r="H32" t="s">
+        <v>255</v>
+      </c>
+      <c r="I32" t="s">
+        <v>202</v>
+      </c>
+      <c r="J32" t="s">
+        <v>129</v>
+      </c>
+      <c r="K32" t="s">
+        <v>130</v>
+      </c>
+      <c r="L32" t="s">
+        <v>1043</v>
+      </c>
+      <c r="M32" t="s">
+        <v>131</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>670</v>
+      </c>
+      <c r="P32" t="s">
         <v>782</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="Q32" t="s">
         <v>841</v>
       </c>
-      <c r="R25" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
-      <c r="A26" t="s">
-        <v>119</v>
-      </c>
-      <c r="B26" t="s">
-        <v>140</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="F26" t="s">
-        <v>347</v>
-      </c>
-      <c r="G26" t="s">
-        <v>300</v>
-      </c>
-      <c r="H26" t="s">
-        <v>253</v>
-      </c>
-      <c r="I26" t="s">
-        <v>200</v>
-      </c>
-      <c r="J26" t="s">
-        <v>141</v>
-      </c>
-      <c r="K26" t="s">
-        <v>142</v>
-      </c>
-      <c r="L26" t="s">
-        <v>143</v>
-      </c>
-      <c r="M26" t="s">
-        <v>144</v>
-      </c>
-      <c r="O26" s="12" t="s">
-        <v>668</v>
-      </c>
-      <c r="P26" t="s">
+      <c r="R32" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="16">
+      <c r="A33" t="s">
+        <v>117</v>
+      </c>
+      <c r="B33" t="s">
+        <v>152</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="D33" t="s">
+        <v>433</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="F33" t="s">
+        <v>350</v>
+      </c>
+      <c r="G33" t="s">
+        <v>303</v>
+      </c>
+      <c r="H33" t="s">
+        <v>256</v>
+      </c>
+      <c r="I33" t="s">
+        <v>203</v>
+      </c>
+      <c r="J33" t="s">
+        <v>153</v>
+      </c>
+      <c r="K33" t="s">
+        <v>154</v>
+      </c>
+      <c r="L33" t="s">
+        <v>155</v>
+      </c>
+      <c r="M33" t="s">
+        <v>156</v>
+      </c>
+      <c r="O33" s="12" t="s">
+        <v>671</v>
+      </c>
+      <c r="P33" t="s">
         <v>783</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="Q33" t="s">
         <v>842</v>
       </c>
-      <c r="R26" t="s">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18">
-      <c r="A27" t="s">
-        <v>119</v>
-      </c>
-      <c r="B27" t="s">
-        <v>145</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>418</v>
-      </c>
-      <c r="D27" t="s">
-        <v>419</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="F27" t="s">
-        <v>348</v>
-      </c>
-      <c r="G27" t="s">
-        <v>301</v>
-      </c>
-      <c r="H27" t="s">
-        <v>254</v>
-      </c>
-      <c r="I27" t="s">
-        <v>201</v>
-      </c>
-      <c r="J27" t="s">
-        <v>146</v>
-      </c>
-      <c r="K27" t="s">
-        <v>147</v>
-      </c>
-      <c r="L27" t="s">
-        <v>148</v>
-      </c>
-      <c r="M27" t="s">
-        <v>149</v>
-      </c>
-      <c r="O27" s="12" t="s">
-        <v>669</v>
-      </c>
-      <c r="P27" t="s">
+      <c r="R33" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="16">
+      <c r="A34" t="s">
+        <v>117</v>
+      </c>
+      <c r="B34" t="s">
+        <v>157</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="F34" t="s">
+        <v>257</v>
+      </c>
+      <c r="G34" t="s">
+        <v>304</v>
+      </c>
+      <c r="H34" t="s">
+        <v>257</v>
+      </c>
+      <c r="I34" t="s">
+        <v>204</v>
+      </c>
+      <c r="J34" t="s">
+        <v>158</v>
+      </c>
+      <c r="K34" t="s">
+        <v>159</v>
+      </c>
+      <c r="L34" t="s">
+        <v>1044</v>
+      </c>
+      <c r="M34" t="s">
+        <v>919</v>
+      </c>
+      <c r="N34" t="s">
+        <v>620</v>
+      </c>
+      <c r="O34" s="12" t="s">
+        <v>672</v>
+      </c>
+      <c r="P34" t="s">
         <v>784</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="Q34" t="s">
         <v>843</v>
       </c>
-      <c r="R27" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18">
-      <c r="A28" t="s">
-        <v>119</v>
-      </c>
-      <c r="B28" t="s">
-        <v>135</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="D28" t="s">
-        <v>422</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="F28" t="s">
-        <v>349</v>
-      </c>
-      <c r="G28" t="s">
-        <v>302</v>
-      </c>
-      <c r="H28" t="s">
-        <v>255</v>
-      </c>
-      <c r="I28" t="s">
-        <v>202</v>
-      </c>
-      <c r="J28" t="s">
-        <v>136</v>
-      </c>
-      <c r="K28" t="s">
-        <v>137</v>
-      </c>
-      <c r="L28" t="s">
-        <v>138</v>
-      </c>
-      <c r="M28" t="s">
-        <v>139</v>
-      </c>
-      <c r="O28" s="12" t="s">
-        <v>670</v>
-      </c>
-      <c r="P28" t="s">
-        <v>785</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>844</v>
-      </c>
-      <c r="R28" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18">
-      <c r="A29" t="s">
-        <v>119</v>
-      </c>
-      <c r="B29" t="s">
-        <v>150</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="D29" t="s">
-        <v>425</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="F29" t="s">
-        <v>350</v>
-      </c>
-      <c r="G29" t="s">
-        <v>303</v>
-      </c>
-      <c r="H29" t="s">
-        <v>256</v>
-      </c>
-      <c r="I29" t="s">
-        <v>203</v>
-      </c>
-      <c r="J29" t="s">
-        <v>151</v>
-      </c>
-      <c r="K29" t="s">
-        <v>152</v>
-      </c>
-      <c r="L29" t="s">
-        <v>153</v>
-      </c>
-      <c r="M29" t="s">
-        <v>154</v>
-      </c>
-      <c r="O29" s="12" t="s">
-        <v>671</v>
-      </c>
-      <c r="P29" t="s">
-        <v>786</v>
-      </c>
-      <c r="Q29" s="13" t="s">
-        <v>845</v>
-      </c>
-      <c r="R29" t="s">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18">
-      <c r="A30" t="s">
-        <v>119</v>
-      </c>
-      <c r="B30" t="s">
-        <v>125</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="D30" t="s">
-        <v>428</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="F30" t="s">
-        <v>351</v>
-      </c>
-      <c r="G30" t="s">
-        <v>304</v>
-      </c>
-      <c r="H30" t="s">
-        <v>257</v>
-      </c>
-      <c r="I30" t="s">
-        <v>204</v>
-      </c>
-      <c r="J30" t="s">
-        <v>126</v>
-      </c>
-      <c r="K30" t="s">
-        <v>127</v>
-      </c>
-      <c r="L30" t="s">
-        <v>128</v>
-      </c>
-      <c r="M30" t="s">
-        <v>129</v>
-      </c>
-      <c r="O30" s="12" t="s">
-        <v>672</v>
-      </c>
-      <c r="P30" t="s">
-        <v>787</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>846</v>
-      </c>
-      <c r="R30" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18">
-      <c r="A31" t="s">
-        <v>119</v>
-      </c>
-      <c r="B31" t="s">
-        <v>120</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="D31" t="s">
-        <v>431</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="F31" t="s">
-        <v>352</v>
-      </c>
-      <c r="G31" t="s">
-        <v>305</v>
-      </c>
-      <c r="H31" t="s">
-        <v>258</v>
-      </c>
-      <c r="I31" t="s">
-        <v>205</v>
-      </c>
-      <c r="J31" t="s">
-        <v>121</v>
-      </c>
-      <c r="K31" t="s">
-        <v>122</v>
-      </c>
-      <c r="L31" t="s">
-        <v>123</v>
-      </c>
-      <c r="M31" t="s">
-        <v>124</v>
-      </c>
-      <c r="O31" s="12" t="s">
-        <v>673</v>
-      </c>
-      <c r="P31" t="s">
-        <v>788</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>847</v>
-      </c>
-      <c r="R31" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18">
-      <c r="A32" t="s">
-        <v>119</v>
-      </c>
-      <c r="B32" t="s">
-        <v>130</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>433</v>
-      </c>
-      <c r="D32" t="s">
-        <v>434</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="F32" t="s">
-        <v>353</v>
-      </c>
-      <c r="G32" t="s">
-        <v>306</v>
-      </c>
-      <c r="H32" t="s">
-        <v>259</v>
-      </c>
-      <c r="I32" t="s">
-        <v>206</v>
-      </c>
-      <c r="J32" t="s">
-        <v>131</v>
-      </c>
-      <c r="K32" t="s">
-        <v>132</v>
-      </c>
-      <c r="L32" t="s">
-        <v>133</v>
-      </c>
-      <c r="M32" t="s">
-        <v>134</v>
-      </c>
-      <c r="O32" s="11" t="s">
-        <v>674</v>
-      </c>
-      <c r="P32" t="s">
-        <v>789</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>848</v>
-      </c>
-      <c r="R32" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18">
-      <c r="A33" t="s">
-        <v>119</v>
-      </c>
-      <c r="B33" t="s">
-        <v>155</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="D33" t="s">
-        <v>437</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>438</v>
-      </c>
-      <c r="F33" t="s">
-        <v>354</v>
-      </c>
-      <c r="G33" t="s">
-        <v>307</v>
-      </c>
-      <c r="H33" t="s">
-        <v>260</v>
-      </c>
-      <c r="I33" t="s">
-        <v>207</v>
-      </c>
-      <c r="J33" t="s">
-        <v>156</v>
-      </c>
-      <c r="K33" t="s">
-        <v>157</v>
-      </c>
-      <c r="L33" t="s">
-        <v>158</v>
-      </c>
-      <c r="M33" t="s">
-        <v>159</v>
-      </c>
-      <c r="O33" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="P33" t="s">
-        <v>790</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>849</v>
-      </c>
-      <c r="R33" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18">
-      <c r="A34" t="s">
-        <v>119</v>
-      </c>
-      <c r="B34" t="s">
-        <v>160</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>440</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="F34" t="s">
-        <v>261</v>
-      </c>
-      <c r="G34" t="s">
-        <v>308</v>
-      </c>
-      <c r="H34" t="s">
-        <v>261</v>
-      </c>
-      <c r="I34" t="s">
-        <v>208</v>
-      </c>
-      <c r="J34" t="s">
-        <v>161</v>
-      </c>
-      <c r="K34" t="s">
-        <v>162</v>
-      </c>
-      <c r="L34" t="s">
-        <v>163</v>
-      </c>
-      <c r="M34" t="s">
-        <v>938</v>
-      </c>
-      <c r="N34" t="s">
-        <v>624</v>
-      </c>
-      <c r="O34" s="12" t="s">
-        <v>676</v>
-      </c>
-      <c r="P34" t="s">
-        <v>791</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>850</v>
-      </c>
       <c r="R34" t="s">
-        <v>973</v>
+        <v>954</v>
       </c>
     </row>
     <row r="35" spans="1:18">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B35" t="s">
-        <v>941</v>
+        <v>922</v>
       </c>
       <c r="D35" s="9"/>
       <c r="F35" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="G35" t="s">
-        <v>966</v>
+        <v>947</v>
       </c>
       <c r="J35" t="s">
-        <v>963</v>
+        <v>944</v>
       </c>
       <c r="K35" t="s">
-        <v>961</v>
+        <v>942</v>
       </c>
       <c r="L35" t="s">
-        <v>959</v>
+        <v>940</v>
       </c>
       <c r="M35" t="s">
-        <v>957</v>
+        <v>938</v>
       </c>
       <c r="O35" s="12"/>
       <c r="R35" t="s">
-        <v>982</v>
+        <v>963</v>
       </c>
     </row>
     <row r="36" spans="1:18">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>942</v>
+        <v>923</v>
       </c>
       <c r="D36" s="9"/>
       <c r="F36" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="G36" t="s">
-        <v>966</v>
+        <v>947</v>
       </c>
       <c r="J36" t="s">
-        <v>964</v>
+        <v>945</v>
       </c>
       <c r="K36" t="s">
-        <v>962</v>
+        <v>943</v>
       </c>
       <c r="L36" t="s">
-        <v>960</v>
+        <v>941</v>
       </c>
       <c r="M36" t="s">
-        <v>958</v>
+        <v>939</v>
       </c>
       <c r="O36" s="12"/>
       <c r="R36" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" ht="15">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="16">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G37"/>
       <c r="H37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="I37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="N37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="O37" s="12" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="P37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="Q37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="R37" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" ht="15">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="16">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="D38" s="10"/>
       <c r="F38" s="3"/>
       <c r="G38"/>
       <c r="L38" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="M38" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="N38" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="P38" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="R38" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" ht="15">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="16">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B39" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="D39" s="10"/>
       <c r="F39" s="3"/>
       <c r="G39"/>
+      <c r="L39" t="s">
+        <v>1045</v>
+      </c>
       <c r="Q39" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="R39" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" ht="15">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="16">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="D40" s="10"/>
       <c r="F40" s="3"/>
       <c r="G40"/>
+      <c r="L40" t="s">
+        <v>1046</v>
+      </c>
       <c r="Q40" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
       <c r="R40" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="16">
       <c r="A41" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" t="s">
+        <v>64</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="F41" t="s">
+        <v>351</v>
+      </c>
+      <c r="G41" t="s">
+        <v>305</v>
+      </c>
+      <c r="H41" t="s">
+        <v>223</v>
+      </c>
+      <c r="I41" t="s">
+        <v>205</v>
+      </c>
+      <c r="J41" t="s">
+        <v>65</v>
+      </c>
+      <c r="K41" t="s">
+        <v>66</v>
+      </c>
+      <c r="L41" t="s">
+        <v>719</v>
+      </c>
+      <c r="M41" t="s">
+        <v>921</v>
+      </c>
+      <c r="N41" t="s">
+        <v>621</v>
+      </c>
+      <c r="O41" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="P41" t="s">
+        <v>786</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>846</v>
+      </c>
+      <c r="R41" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="16">
+      <c r="A42" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="G42" t="s">
+        <v>306</v>
+      </c>
+      <c r="H42" t="s">
+        <v>222</v>
+      </c>
+      <c r="I42" t="s">
+        <v>206</v>
+      </c>
+      <c r="J42" t="s">
         <v>49</v>
       </c>
-      <c r="B41" t="s">
-        <v>66</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="E41" s="9" t="s">
+      <c r="K42" t="s">
+        <v>50</v>
+      </c>
+      <c r="L42" t="s">
+        <v>51</v>
+      </c>
+      <c r="M42" t="s">
+        <v>920</v>
+      </c>
+      <c r="N42" t="s">
+        <v>622</v>
+      </c>
+      <c r="O42" s="11" t="s">
+        <v>674</v>
+      </c>
+      <c r="P42" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>847</v>
+      </c>
+      <c r="R42" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="16">
+      <c r="A43" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" t="s">
+        <v>181</v>
+      </c>
+      <c r="C43" s="9" t="s">
         <v>446</v>
       </c>
-      <c r="F41" t="s">
-        <v>355</v>
-      </c>
-      <c r="G41" t="s">
-        <v>309</v>
-      </c>
-      <c r="H41" t="s">
-        <v>227</v>
-      </c>
-      <c r="I41" t="s">
-        <v>209</v>
-      </c>
-      <c r="J41" t="s">
-        <v>67</v>
-      </c>
-      <c r="K41" t="s">
-        <v>68</v>
-      </c>
-      <c r="L41" t="s">
-        <v>724</v>
-      </c>
-      <c r="M41" t="s">
-        <v>940</v>
-      </c>
-      <c r="N41" t="s">
-        <v>625</v>
-      </c>
-      <c r="O41" s="12" t="s">
-        <v>677</v>
-      </c>
-      <c r="P41" t="s">
-        <v>793</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>853</v>
-      </c>
-      <c r="R41" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18">
-      <c r="A42" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" t="s">
-        <v>50</v>
-      </c>
-      <c r="C42" s="9" t="s">
+      <c r="D43" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="E43" s="9" t="s">
         <v>447</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="G42" t="s">
-        <v>310</v>
-      </c>
-      <c r="H42" t="s">
-        <v>226</v>
-      </c>
-      <c r="I42" t="s">
-        <v>210</v>
-      </c>
-      <c r="J42" t="s">
-        <v>51</v>
-      </c>
-      <c r="K42" t="s">
-        <v>52</v>
-      </c>
-      <c r="L42" t="s">
-        <v>53</v>
-      </c>
-      <c r="M42" t="s">
-        <v>939</v>
-      </c>
-      <c r="N42" t="s">
-        <v>626</v>
-      </c>
-      <c r="O42" s="11" t="s">
-        <v>678</v>
-      </c>
-      <c r="P42" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>854</v>
-      </c>
-      <c r="R42" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18">
-      <c r="A43" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" t="s">
-        <v>185</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>451</v>
       </c>
       <c r="G43"/>
       <c r="H43" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I43" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="N43" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P43" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="R43" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="16">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B44" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="G44" t="s">
+        <v>307</v>
+      </c>
+      <c r="H44" t="s">
+        <v>224</v>
+      </c>
+      <c r="I44" t="s">
+        <v>207</v>
+      </c>
+      <c r="J44" t="s">
+        <v>61</v>
+      </c>
+      <c r="K44" t="s">
+        <v>60</v>
+      </c>
+      <c r="L44" t="s">
         <v>62</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="M44" t="s">
+        <v>63</v>
+      </c>
+      <c r="N44" t="s">
+        <v>623</v>
+      </c>
+      <c r="O44" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="P44" t="s">
+        <v>787</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>848</v>
+      </c>
+      <c r="R44" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="16">
+      <c r="A45" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" t="s">
+        <v>183</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="D45" s="9" t="s">
         <v>452</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="E45" s="9" t="s">
         <v>453</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="G44" t="s">
-        <v>311</v>
-      </c>
-      <c r="H44" t="s">
-        <v>228</v>
-      </c>
-      <c r="I44" t="s">
-        <v>211</v>
-      </c>
-      <c r="J44" t="s">
-        <v>63</v>
-      </c>
-      <c r="K44" t="s">
-        <v>62</v>
-      </c>
-      <c r="L44" t="s">
-        <v>64</v>
-      </c>
-      <c r="M44" t="s">
-        <v>65</v>
-      </c>
-      <c r="N44" t="s">
-        <v>627</v>
-      </c>
-      <c r="O44" s="12" t="s">
-        <v>679</v>
-      </c>
-      <c r="P44" t="s">
-        <v>794</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>855</v>
-      </c>
-      <c r="R44" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18">
-      <c r="A45" t="s">
-        <v>49</v>
-      </c>
-      <c r="B45" t="s">
-        <v>187</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>455</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>457</v>
       </c>
       <c r="G45"/>
       <c r="H45" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I45" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="N45" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P45" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="R45" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="16">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B46" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="G46" t="s">
+        <v>308</v>
+      </c>
+      <c r="H46" t="s">
+        <v>225</v>
+      </c>
+      <c r="I46" t="s">
+        <v>56</v>
+      </c>
+      <c r="J46" t="s">
+        <v>57</v>
+      </c>
+      <c r="K46" t="s">
+        <v>56</v>
+      </c>
+      <c r="L46" t="s">
         <v>58</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="M46" t="s">
+        <v>59</v>
+      </c>
+      <c r="N46" t="s">
+        <v>624</v>
+      </c>
+      <c r="O46" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="P46" t="s">
+        <v>56</v>
+      </c>
+      <c r="R46" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="16">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" t="s">
+        <v>186</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="D47" s="9" t="s">
         <v>458</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="E47" s="9" t="s">
         <v>459</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="G46" t="s">
-        <v>312</v>
-      </c>
-      <c r="H46" t="s">
-        <v>229</v>
-      </c>
-      <c r="I46" t="s">
-        <v>58</v>
-      </c>
-      <c r="J46" t="s">
-        <v>59</v>
-      </c>
-      <c r="K46" t="s">
-        <v>58</v>
-      </c>
-      <c r="L46" t="s">
-        <v>60</v>
-      </c>
-      <c r="M46" t="s">
-        <v>61</v>
-      </c>
-      <c r="N46" t="s">
-        <v>628</v>
-      </c>
-      <c r="O46" s="12" t="s">
-        <v>680</v>
-      </c>
-      <c r="P46" t="s">
-        <v>58</v>
-      </c>
-      <c r="R46" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18">
-      <c r="A47" t="s">
-        <v>49</v>
-      </c>
-      <c r="B47" t="s">
-        <v>190</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>461</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>463</v>
       </c>
       <c r="G47"/>
       <c r="I47" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="P47" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="R47" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="16">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="G48"/>
       <c r="I48" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="P48" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="R48" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="16">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="G49"/>
       <c r="I49" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P49" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
       <c r="R49" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="50" spans="1:18">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="D50" s="9"/>
       <c r="G50"/>
       <c r="P50" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="R50" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
     </row>
     <row r="51" spans="1:18">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="D51" s="9"/>
       <c r="G51"/>
       <c r="P51" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="R51" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
     </row>
     <row r="52" spans="1:18">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B52" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="D52" s="9"/>
       <c r="G52"/>
       <c r="L52" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="M52" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="P52" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="Q52" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
       <c r="R52" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="16">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B53" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="G53"/>
       <c r="I53" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N53" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="P53" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="R53" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="16">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B54" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="G54"/>
       <c r="H54" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I54" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="N54" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="P54" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="R54" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="16">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B55" t="s">
+        <v>52</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="F55" t="s">
+        <v>355</v>
+      </c>
+      <c r="G55" t="s">
+        <v>309</v>
+      </c>
+      <c r="H55" t="s">
+        <v>226</v>
+      </c>
+      <c r="I55" t="s">
+        <v>208</v>
+      </c>
+      <c r="J55" t="s">
+        <v>53</v>
+      </c>
+      <c r="K55" t="s">
+        <v>52</v>
+      </c>
+      <c r="L55" t="s">
         <v>54</v>
       </c>
-      <c r="C55" s="9" t="s">
-        <v>475</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="F55" t="s">
-        <v>359</v>
-      </c>
-      <c r="G55" t="s">
-        <v>313</v>
-      </c>
-      <c r="H55" t="s">
-        <v>230</v>
-      </c>
-      <c r="I55" t="s">
-        <v>212</v>
-      </c>
-      <c r="J55" t="s">
+      <c r="M55" t="s">
         <v>55</v>
       </c>
-      <c r="K55" t="s">
-        <v>54</v>
-      </c>
-      <c r="L55" t="s">
-        <v>56</v>
-      </c>
-      <c r="M55" t="s">
-        <v>57</v>
-      </c>
       <c r="N55" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="O55" s="12" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="P55" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="R55" t="s">
-        <v>990</v>
+        <v>971</v>
       </c>
     </row>
     <row r="56" spans="1:18">
       <c r="A56" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="D56" s="9"/>
       <c r="G56"/>
       <c r="L56" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="O56" s="11" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="P56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="R56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="57" spans="1:18">
       <c r="A57" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B57" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="D57" s="9"/>
       <c r="G57"/>
       <c r="L57" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="M57" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="N57" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="P57" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="R57" t="s">
-        <v>991</v>
+        <v>972</v>
       </c>
     </row>
     <row r="58" spans="1:18">
       <c r="A58" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B58" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="C58"/>
       <c r="E58"/>
       <c r="G58"/>
       <c r="L58" t="s">
-        <v>904</v>
+        <v>1047</v>
       </c>
       <c r="R58" t="s">
-        <v>992</v>
+        <v>973</v>
       </c>
     </row>
     <row r="59" spans="1:18">
       <c r="A59" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B59" t="s">
-        <v>892</v>
+        <v>885</v>
       </c>
       <c r="C59"/>
       <c r="E59"/>
       <c r="G59"/>
       <c r="L59" t="s">
-        <v>905</v>
+        <v>1048</v>
       </c>
       <c r="R59" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
     </row>
     <row r="60" spans="1:18">
       <c r="A60" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B60" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="C60"/>
       <c r="E60"/>
       <c r="G60"/>
       <c r="L60" t="s">
-        <v>906</v>
+        <v>1049</v>
       </c>
       <c r="R60" t="s">
-        <v>994</v>
+        <v>975</v>
       </c>
     </row>
     <row r="61" spans="1:18">
       <c r="A61" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B61" t="s">
-        <v>894</v>
+        <v>887</v>
       </c>
       <c r="C61"/>
       <c r="E61"/>
       <c r="G61"/>
       <c r="L61" t="s">
-        <v>907</v>
+        <v>1050</v>
       </c>
       <c r="R61" t="s">
-        <v>995</v>
+        <v>976</v>
       </c>
     </row>
     <row r="62" spans="1:18">
       <c r="A62" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B62" t="s">
-        <v>895</v>
+        <v>888</v>
       </c>
       <c r="C62"/>
       <c r="E62"/>
       <c r="G62"/>
       <c r="L62" t="s">
-        <v>908</v>
+        <v>1051</v>
       </c>
       <c r="R62" t="s">
-        <v>996</v>
+        <v>977</v>
       </c>
     </row>
     <row r="63" spans="1:18">
       <c r="A63" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B63" t="s">
-        <v>896</v>
+        <v>889</v>
       </c>
       <c r="C63"/>
       <c r="E63"/>
       <c r="G63"/>
       <c r="L63" t="s">
-        <v>909</v>
+        <v>897</v>
       </c>
       <c r="R63" t="s">
-        <v>997</v>
+        <v>978</v>
       </c>
     </row>
     <row r="64" spans="1:18">
       <c r="A64" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B64" t="s">
-        <v>897</v>
+        <v>890</v>
       </c>
       <c r="C64"/>
       <c r="E64"/>
       <c r="G64"/>
       <c r="L64" t="s">
-        <v>910</v>
+        <v>1052</v>
       </c>
       <c r="R64" t="s">
-        <v>998</v>
+        <v>979</v>
       </c>
     </row>
     <row r="65" spans="1:18">
       <c r="A65" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B65" t="s">
-        <v>898</v>
+        <v>891</v>
       </c>
       <c r="C65"/>
       <c r="E65"/>
       <c r="G65"/>
       <c r="L65" t="s">
-        <v>911</v>
+        <v>1054</v>
       </c>
       <c r="R65" t="s">
-        <v>999</v>
+        <v>980</v>
       </c>
     </row>
     <row r="66" spans="1:18">
       <c r="A66" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B66" t="s">
-        <v>899</v>
+        <v>892</v>
       </c>
       <c r="C66"/>
       <c r="E66"/>
       <c r="G66"/>
       <c r="L66" t="s">
-        <v>912</v>
+        <v>1055</v>
       </c>
       <c r="R66" t="s">
-        <v>1000</v>
+        <v>981</v>
       </c>
     </row>
     <row r="67" spans="1:18">
       <c r="A67" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B67" t="s">
-        <v>900</v>
+        <v>893</v>
       </c>
       <c r="C67"/>
       <c r="E67"/>
       <c r="G67"/>
       <c r="L67" t="s">
-        <v>913</v>
+        <v>1056</v>
       </c>
       <c r="R67" t="s">
-        <v>1001</v>
+        <v>982</v>
       </c>
     </row>
     <row r="68" spans="1:18">
       <c r="A68" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B68" t="s">
-        <v>901</v>
+        <v>894</v>
       </c>
       <c r="C68"/>
       <c r="E68"/>
       <c r="G68"/>
       <c r="L68" t="s">
-        <v>914</v>
+        <v>1057</v>
       </c>
       <c r="R68" t="s">
-        <v>1002</v>
+        <v>983</v>
       </c>
     </row>
     <row r="69" spans="1:18">
       <c r="A69" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B69" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="C69"/>
       <c r="E69"/>
       <c r="G69"/>
       <c r="L69" t="s">
-        <v>915</v>
+        <v>1053</v>
       </c>
       <c r="R69" t="s">
-        <v>1003</v>
+        <v>984</v>
       </c>
     </row>
     <row r="70" spans="1:18">
       <c r="A70" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B70" t="s">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="C70"/>
       <c r="E70"/>
       <c r="G70"/>
       <c r="L70" t="s">
-        <v>916</v>
+        <v>1058</v>
       </c>
       <c r="R70" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="71" spans="1:18">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" ht="16">
       <c r="A71" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B71" t="s">
+        <v>100</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="G71" t="s">
+        <v>310</v>
+      </c>
+      <c r="H71" t="s">
+        <v>258</v>
+      </c>
+      <c r="I71" t="s">
+        <v>209</v>
+      </c>
+      <c r="J71" t="s">
+        <v>101</v>
+      </c>
+      <c r="K71" t="s">
         <v>102</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="L71" t="s">
+        <v>103</v>
+      </c>
+      <c r="M71" t="s">
+        <v>104</v>
+      </c>
+      <c r="N71" t="s">
+        <v>627</v>
+      </c>
+      <c r="O71" s="12" t="s">
+        <v>679</v>
+      </c>
+      <c r="P71" t="s">
+        <v>793</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>850</v>
+      </c>
+      <c r="R71" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" ht="16">
+      <c r="A72" t="s">
+        <v>67</v>
+      </c>
+      <c r="B72" t="s">
+        <v>241</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="E72" s="9" t="s">
         <v>478</v>
       </c>
-      <c r="D71" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="E71" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="G71" t="s">
-        <v>314</v>
-      </c>
-      <c r="H71" t="s">
-        <v>262</v>
-      </c>
-      <c r="I71" t="s">
-        <v>213</v>
-      </c>
-      <c r="J71" t="s">
-        <v>103</v>
-      </c>
-      <c r="K71" t="s">
-        <v>104</v>
-      </c>
-      <c r="L71" t="s">
-        <v>105</v>
-      </c>
-      <c r="M71" t="s">
-        <v>106</v>
-      </c>
-      <c r="N71" t="s">
-        <v>631</v>
-      </c>
-      <c r="O71" s="12" t="s">
-        <v>683</v>
-      </c>
-      <c r="P71" t="s">
-        <v>800</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>857</v>
-      </c>
-      <c r="R71" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="72" spans="1:18">
-      <c r="A72" t="s">
-        <v>69</v>
-      </c>
-      <c r="B72" t="s">
-        <v>245</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="E72" s="9" t="s">
-        <v>482</v>
-      </c>
       <c r="F72" s="2" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="G72"/>
       <c r="H72" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="J72" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="L72" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="N72" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="O72" s="12" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="P72" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="Q72" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="R72" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="73" spans="1:18">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" ht="16">
       <c r="A73" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B73" t="s">
+        <v>105</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="E73" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="F73" t="s">
+        <v>358</v>
+      </c>
+      <c r="G73" t="s">
+        <v>311</v>
+      </c>
+      <c r="H73" t="s">
+        <v>260</v>
+      </c>
+      <c r="I73" t="s">
+        <v>210</v>
+      </c>
+      <c r="J73" t="s">
+        <v>106</v>
+      </c>
+      <c r="K73" t="s">
         <v>107</v>
       </c>
-      <c r="C73" s="9" t="s">
+      <c r="L73" t="s">
+        <v>108</v>
+      </c>
+      <c r="M73" t="s">
+        <v>109</v>
+      </c>
+      <c r="N73" t="s">
+        <v>629</v>
+      </c>
+      <c r="O73" s="12" t="s">
+        <v>681</v>
+      </c>
+      <c r="P73" t="s">
+        <v>795</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>852</v>
+      </c>
+      <c r="R73" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="16">
+      <c r="A74" t="s">
+        <v>67</v>
+      </c>
+      <c r="B74" t="s">
+        <v>242</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="E74" s="9" t="s">
         <v>483</v>
       </c>
-      <c r="D73" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="E73" s="9" t="s">
-        <v>484</v>
-      </c>
-      <c r="F73" t="s">
-        <v>362</v>
-      </c>
-      <c r="G73" t="s">
-        <v>315</v>
-      </c>
-      <c r="H73" t="s">
-        <v>264</v>
-      </c>
-      <c r="I73" t="s">
-        <v>214</v>
-      </c>
-      <c r="J73" t="s">
-        <v>108</v>
-      </c>
-      <c r="K73" t="s">
-        <v>109</v>
-      </c>
-      <c r="L73" t="s">
-        <v>110</v>
-      </c>
-      <c r="M73" t="s">
-        <v>111</v>
-      </c>
-      <c r="N73" t="s">
-        <v>633</v>
-      </c>
-      <c r="O73" s="12" t="s">
-        <v>685</v>
-      </c>
-      <c r="P73" t="s">
-        <v>802</v>
-      </c>
-      <c r="Q73" t="s">
-        <v>859</v>
-      </c>
-      <c r="R73" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="74" spans="1:18">
-      <c r="A74" t="s">
-        <v>69</v>
-      </c>
-      <c r="B74" t="s">
-        <v>246</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>485</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="E74" s="9" t="s">
-        <v>487</v>
-      </c>
       <c r="F74" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="G74"/>
       <c r="H74" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="J74" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="L74" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="N74" t="s">
+        <v>630</v>
+      </c>
+      <c r="O74" s="12" t="s">
+        <v>682</v>
+      </c>
+      <c r="P74" t="s">
+        <v>796</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>853</v>
+      </c>
+      <c r="R74" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="16">
+      <c r="A75" t="s">
+        <v>67</v>
+      </c>
+      <c r="B75" t="s">
+        <v>68</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="G75" t="s">
+        <v>312</v>
+      </c>
+      <c r="H75" t="s">
+        <v>263</v>
+      </c>
+      <c r="I75" t="s">
+        <v>211</v>
+      </c>
+      <c r="J75" t="s">
+        <v>69</v>
+      </c>
+      <c r="K75" t="s">
+        <v>70</v>
+      </c>
+      <c r="L75" t="s">
+        <v>71</v>
+      </c>
+      <c r="M75" t="s">
+        <v>72</v>
+      </c>
+      <c r="N75" t="s">
+        <v>631</v>
+      </c>
+      <c r="O75" s="11" t="s">
+        <v>683</v>
+      </c>
+      <c r="P75" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>854</v>
+      </c>
+      <c r="R75" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="16">
+      <c r="A76" t="s">
+        <v>67</v>
+      </c>
+      <c r="B76" t="s">
+        <v>98</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="E76" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="G76" t="s">
+        <v>313</v>
+      </c>
+      <c r="H76" t="s">
+        <v>227</v>
+      </c>
+      <c r="I76" t="s">
+        <v>577</v>
+      </c>
+      <c r="J76" t="s">
+        <v>267</v>
+      </c>
+      <c r="K76" t="s">
+        <v>98</v>
+      </c>
+      <c r="L76" t="s">
+        <v>99</v>
+      </c>
+      <c r="M76" t="s">
+        <v>760</v>
+      </c>
+      <c r="N76" t="s">
+        <v>98</v>
+      </c>
+      <c r="O76" s="12" t="s">
+        <v>684</v>
+      </c>
+      <c r="P76" t="s">
+        <v>797</v>
+      </c>
+      <c r="R76" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="16">
+      <c r="A77" t="s">
+        <v>67</v>
+      </c>
+      <c r="B77" t="s">
+        <v>89</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="F77" t="s">
+        <v>228</v>
+      </c>
+      <c r="G77" t="s">
+        <v>314</v>
+      </c>
+      <c r="H77" t="s">
+        <v>228</v>
+      </c>
+      <c r="I77" t="s">
+        <v>89</v>
+      </c>
+      <c r="J77" t="s">
+        <v>90</v>
+      </c>
+      <c r="K77" t="s">
+        <v>89</v>
+      </c>
+      <c r="L77" t="s">
+        <v>89</v>
+      </c>
+      <c r="M77" t="s">
+        <v>90</v>
+      </c>
+      <c r="N77" t="s">
+        <v>632</v>
+      </c>
+      <c r="O77" s="11" t="s">
+        <v>685</v>
+      </c>
+      <c r="P77" t="s">
+        <v>798</v>
+      </c>
+      <c r="R77" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="16">
+      <c r="A78" t="s">
+        <v>67</v>
+      </c>
+      <c r="B78" t="s">
+        <v>574</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="G78" t="s">
+        <v>315</v>
+      </c>
+      <c r="H78" t="s">
+        <v>229</v>
+      </c>
+      <c r="I78" t="s">
+        <v>578</v>
+      </c>
+      <c r="J78" t="s">
+        <v>580</v>
+      </c>
+      <c r="K78" t="s">
+        <v>83</v>
+      </c>
+      <c r="L78" t="s">
+        <v>582</v>
+      </c>
+      <c r="M78" t="s">
+        <v>84</v>
+      </c>
+      <c r="N78" t="s">
+        <v>633</v>
+      </c>
+      <c r="O78" s="11" t="s">
+        <v>686</v>
+      </c>
+      <c r="P78" t="s">
+        <v>799</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>855</v>
+      </c>
+      <c r="R78" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" ht="16">
+      <c r="A79" t="s">
+        <v>67</v>
+      </c>
+      <c r="B79" t="s">
+        <v>85</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="G79" t="s">
+        <v>316</v>
+      </c>
+      <c r="H79" t="s">
+        <v>230</v>
+      </c>
+      <c r="I79" t="s">
+        <v>85</v>
+      </c>
+      <c r="J79" t="s">
+        <v>86</v>
+      </c>
+      <c r="K79" t="s">
+        <v>85</v>
+      </c>
+      <c r="L79" t="s">
+        <v>581</v>
+      </c>
+      <c r="M79" t="s">
+        <v>86</v>
+      </c>
+      <c r="N79" t="s">
         <v>634</v>
       </c>
-      <c r="O74" s="12" t="s">
-        <v>686</v>
-      </c>
-      <c r="P74" t="s">
-        <v>803</v>
-      </c>
-      <c r="Q74" t="s">
-        <v>860</v>
-      </c>
-      <c r="R74" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="75" spans="1:18">
-      <c r="A75" t="s">
-        <v>69</v>
-      </c>
-      <c r="B75" t="s">
-        <v>70</v>
-      </c>
-      <c r="C75" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="E75" s="9" t="s">
-        <v>490</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="G75" t="s">
-        <v>316</v>
-      </c>
-      <c r="H75" t="s">
-        <v>267</v>
-      </c>
-      <c r="I75" t="s">
-        <v>215</v>
-      </c>
-      <c r="J75" t="s">
-        <v>71</v>
-      </c>
-      <c r="K75" t="s">
-        <v>72</v>
-      </c>
-      <c r="L75" t="s">
-        <v>73</v>
-      </c>
-      <c r="M75" t="s">
-        <v>74</v>
-      </c>
-      <c r="N75" t="s">
+      <c r="O79" s="11" t="s">
+        <v>687</v>
+      </c>
+      <c r="P79" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>856</v>
+      </c>
+      <c r="R79" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="16">
+      <c r="A80" t="s">
+        <v>67</v>
+      </c>
+      <c r="B80" t="s">
+        <v>87</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="F80" t="s">
+        <v>231</v>
+      </c>
+      <c r="G80" t="s">
+        <v>317</v>
+      </c>
+      <c r="H80" t="s">
+        <v>231</v>
+      </c>
+      <c r="I80" t="s">
+        <v>87</v>
+      </c>
+      <c r="J80" t="s">
+        <v>88</v>
+      </c>
+      <c r="K80" t="s">
+        <v>87</v>
+      </c>
+      <c r="L80" t="s">
+        <v>87</v>
+      </c>
+      <c r="M80" t="s">
+        <v>88</v>
+      </c>
+      <c r="N80" t="s">
         <v>635</v>
       </c>
-      <c r="O75" s="11" t="s">
-        <v>687</v>
-      </c>
-      <c r="P75" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q75" t="s">
-        <v>861</v>
-      </c>
-      <c r="R75" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18">
-      <c r="A76" t="s">
-        <v>69</v>
-      </c>
-      <c r="B76" t="s">
-        <v>100</v>
-      </c>
-      <c r="C76" s="9" t="s">
-        <v>491</v>
-      </c>
-      <c r="D76" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="E76" s="9" t="s">
-        <v>493</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="G76" t="s">
-        <v>317</v>
-      </c>
-      <c r="H76" t="s">
-        <v>231</v>
-      </c>
-      <c r="I76" t="s">
-        <v>581</v>
-      </c>
-      <c r="J76" t="s">
-        <v>271</v>
-      </c>
-      <c r="K76" t="s">
-        <v>100</v>
-      </c>
-      <c r="L76" t="s">
-        <v>101</v>
-      </c>
-      <c r="M76" t="s">
-        <v>767</v>
-      </c>
-      <c r="N76" t="s">
-        <v>100</v>
-      </c>
-      <c r="O76" s="12" t="s">
+      <c r="O80" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="P76" t="s">
-        <v>804</v>
-      </c>
-      <c r="R76" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="77" spans="1:18">
-      <c r="A77" t="s">
-        <v>69</v>
-      </c>
-      <c r="B77" t="s">
-        <v>91</v>
-      </c>
-      <c r="C77" s="9" t="s">
-        <v>494</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>495</v>
-      </c>
-      <c r="E77" s="9" t="s">
-        <v>496</v>
-      </c>
-      <c r="F77" t="s">
-        <v>232</v>
-      </c>
-      <c r="G77" t="s">
-        <v>318</v>
-      </c>
-      <c r="H77" t="s">
-        <v>232</v>
-      </c>
-      <c r="I77" t="s">
-        <v>91</v>
-      </c>
-      <c r="J77" t="s">
-        <v>92</v>
-      </c>
-      <c r="K77" t="s">
-        <v>91</v>
-      </c>
-      <c r="L77" t="s">
-        <v>91</v>
-      </c>
-      <c r="M77" t="s">
-        <v>92</v>
-      </c>
-      <c r="N77" t="s">
-        <v>636</v>
-      </c>
-      <c r="O77" s="11" t="s">
-        <v>689</v>
-      </c>
-      <c r="P77" t="s">
-        <v>805</v>
-      </c>
-      <c r="R77" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="78" spans="1:18">
-      <c r="A78" t="s">
-        <v>69</v>
-      </c>
-      <c r="B78" t="s">
-        <v>578</v>
-      </c>
-      <c r="C78" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="D78" s="9" t="s">
-        <v>498</v>
-      </c>
-      <c r="E78" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="G78" t="s">
-        <v>319</v>
-      </c>
-      <c r="H78" t="s">
-        <v>233</v>
-      </c>
-      <c r="I78" t="s">
-        <v>582</v>
-      </c>
-      <c r="J78" t="s">
-        <v>584</v>
-      </c>
-      <c r="K78" t="s">
-        <v>85</v>
-      </c>
-      <c r="L78" t="s">
-        <v>586</v>
-      </c>
-      <c r="M78" t="s">
-        <v>86</v>
-      </c>
-      <c r="N78" t="s">
-        <v>637</v>
-      </c>
-      <c r="O78" s="11" t="s">
-        <v>690</v>
-      </c>
-      <c r="P78" t="s">
-        <v>806</v>
-      </c>
-      <c r="Q78" t="s">
-        <v>862</v>
-      </c>
-      <c r="R78" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="79" spans="1:18">
-      <c r="A79" t="s">
-        <v>69</v>
-      </c>
-      <c r="B79" t="s">
+      <c r="P80" t="s">
+        <v>800</v>
+      </c>
+      <c r="R80" t="s">
         <v>87</v>
       </c>
-      <c r="C79" s="9" t="s">
-        <v>500</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>501</v>
-      </c>
-      <c r="E79" s="9" t="s">
+    </row>
+    <row r="81" spans="1:18" ht="16">
+      <c r="A81" t="s">
+        <v>67</v>
+      </c>
+      <c r="B81" t="s">
+        <v>237</v>
+      </c>
+      <c r="C81" s="9" t="s">
         <v>502</v>
       </c>
-      <c r="F79" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="G79" t="s">
-        <v>320</v>
-      </c>
-      <c r="H79" t="s">
-        <v>234</v>
-      </c>
-      <c r="I79" t="s">
-        <v>87</v>
-      </c>
-      <c r="J79" t="s">
-        <v>88</v>
-      </c>
-      <c r="K79" t="s">
-        <v>87</v>
-      </c>
-      <c r="L79" t="s">
-        <v>585</v>
-      </c>
-      <c r="M79" t="s">
-        <v>88</v>
-      </c>
-      <c r="N79" t="s">
-        <v>638</v>
-      </c>
-      <c r="O79" s="11" t="s">
-        <v>691</v>
-      </c>
-      <c r="P79" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q79" t="s">
-        <v>863</v>
-      </c>
-      <c r="R79" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="80" spans="1:18">
-      <c r="A80" t="s">
-        <v>69</v>
-      </c>
-      <c r="B80" t="s">
-        <v>89</v>
-      </c>
-      <c r="C80" s="9" t="s">
+      <c r="D81" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="E81" s="9" t="s">
         <v>503</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>504</v>
-      </c>
-      <c r="E80" s="9" t="s">
-        <v>505</v>
-      </c>
-      <c r="F80" t="s">
-        <v>235</v>
-      </c>
-      <c r="G80" t="s">
-        <v>321</v>
-      </c>
-      <c r="H80" t="s">
-        <v>235</v>
-      </c>
-      <c r="I80" t="s">
-        <v>89</v>
-      </c>
-      <c r="J80" t="s">
-        <v>90</v>
-      </c>
-      <c r="K80" t="s">
-        <v>89</v>
-      </c>
-      <c r="L80" t="s">
-        <v>89</v>
-      </c>
-      <c r="M80" t="s">
-        <v>90</v>
-      </c>
-      <c r="N80" t="s">
-        <v>639</v>
-      </c>
-      <c r="O80" s="11" t="s">
-        <v>692</v>
-      </c>
-      <c r="P80" t="s">
-        <v>807</v>
-      </c>
-      <c r="R80" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="81" spans="1:18">
-      <c r="A81" t="s">
-        <v>69</v>
-      </c>
-      <c r="B81" t="s">
-        <v>241</v>
-      </c>
-      <c r="C81" s="9" t="s">
-        <v>506</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>506</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>507</v>
       </c>
       <c r="G81"/>
       <c r="J81" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="N81" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="P81" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="R81" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="82" spans="1:18">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" ht="16">
       <c r="A82" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B82" t="s">
+        <v>110</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="G82" t="s">
+        <v>318</v>
+      </c>
+      <c r="I82" t="s">
+        <v>212</v>
+      </c>
+      <c r="J82" t="s">
+        <v>111</v>
+      </c>
+      <c r="K82" t="s">
         <v>112</v>
       </c>
-      <c r="C82" s="9" t="s">
+      <c r="L82" t="s">
+        <v>113</v>
+      </c>
+      <c r="M82" t="s">
+        <v>114</v>
+      </c>
+      <c r="N82" t="s">
+        <v>636</v>
+      </c>
+      <c r="O82" s="11" t="s">
+        <v>689</v>
+      </c>
+      <c r="P82" t="s">
+        <v>801</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>857</v>
+      </c>
+      <c r="R82" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" ht="16">
+      <c r="A83" t="s">
+        <v>67</v>
+      </c>
+      <c r="B83" t="s">
+        <v>236</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="G83" t="s">
+        <v>318</v>
+      </c>
+      <c r="I83" t="s">
+        <v>212</v>
+      </c>
+      <c r="J83" t="s">
+        <v>111</v>
+      </c>
+      <c r="K83" t="s">
+        <v>112</v>
+      </c>
+      <c r="L83" t="s">
+        <v>113</v>
+      </c>
+      <c r="M83" t="s">
+        <v>114</v>
+      </c>
+      <c r="N83" t="s">
+        <v>636</v>
+      </c>
+      <c r="O83" s="11" t="s">
+        <v>689</v>
+      </c>
+      <c r="P83" t="s">
+        <v>802</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>857</v>
+      </c>
+      <c r="R83" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" ht="16">
+      <c r="A84" t="s">
+        <v>67</v>
+      </c>
+      <c r="B84" t="s">
+        <v>239</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="D84" s="9" t="s">
         <v>508</v>
       </c>
-      <c r="D82" s="9" t="s">
+      <c r="E84" s="9" t="s">
         <v>509</v>
-      </c>
-      <c r="E82" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="G82" t="s">
-        <v>322</v>
-      </c>
-      <c r="I82" t="s">
-        <v>216</v>
-      </c>
-      <c r="J82" t="s">
-        <v>113</v>
-      </c>
-      <c r="K82" t="s">
-        <v>114</v>
-      </c>
-      <c r="L82" t="s">
-        <v>115</v>
-      </c>
-      <c r="M82" t="s">
-        <v>116</v>
-      </c>
-      <c r="N82" t="s">
-        <v>640</v>
-      </c>
-      <c r="O82" s="11" t="s">
-        <v>693</v>
-      </c>
-      <c r="P82" t="s">
-        <v>808</v>
-      </c>
-      <c r="Q82" t="s">
-        <v>864</v>
-      </c>
-      <c r="R82" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="83" spans="1:18">
-      <c r="A83" t="s">
-        <v>69</v>
-      </c>
-      <c r="B83" t="s">
-        <v>240</v>
-      </c>
-      <c r="C83" s="9" t="s">
-        <v>508</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="E83" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="G83" t="s">
-        <v>322</v>
-      </c>
-      <c r="I83" t="s">
-        <v>216</v>
-      </c>
-      <c r="J83" t="s">
-        <v>113</v>
-      </c>
-      <c r="K83" t="s">
-        <v>114</v>
-      </c>
-      <c r="L83" t="s">
-        <v>115</v>
-      </c>
-      <c r="M83" t="s">
-        <v>116</v>
-      </c>
-      <c r="N83" t="s">
-        <v>640</v>
-      </c>
-      <c r="O83" s="11" t="s">
-        <v>693</v>
-      </c>
-      <c r="P83" t="s">
-        <v>809</v>
-      </c>
-      <c r="Q83" t="s">
-        <v>864</v>
-      </c>
-      <c r="R83" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="84" spans="1:18">
-      <c r="A84" t="s">
-        <v>69</v>
-      </c>
-      <c r="B84" t="s">
-        <v>243</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>511</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>512</v>
-      </c>
-      <c r="E84" s="9" t="s">
-        <v>513</v>
       </c>
       <c r="G84"/>
       <c r="J84" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="L84" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="N84" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="O84" s="11" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="P84" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="Q84" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="R84" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="85" spans="1:18">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" ht="16">
       <c r="A85" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B85" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="G85"/>
       <c r="J85" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="L85" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="N85" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="O85" s="12" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="P85" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="Q85" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="R85" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="86" spans="1:18">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" ht="16">
       <c r="A86" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B86" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="G86"/>
       <c r="J86" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="L86" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="N86" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="O86" s="12" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="P86" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="Q86" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="R86" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="87" spans="1:18">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" ht="16">
       <c r="A87" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B87" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="G87" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="I87" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="J87" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="K87" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="L87" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="M87" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N87" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="O87" s="12" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="P87" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="Q87" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="R87" t="s">
-        <v>1015</v>
+        <v>996</v>
       </c>
     </row>
     <row r="88" spans="1:18">
       <c r="A88" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B88" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="D88" s="9"/>
       <c r="F88" t="s">
+        <v>584</v>
+      </c>
+      <c r="G88" t="s">
+        <v>583</v>
+      </c>
+      <c r="H88" t="s">
+        <v>586</v>
+      </c>
+      <c r="I88" t="s">
+        <v>587</v>
+      </c>
+      <c r="J88" t="s">
+        <v>589</v>
+      </c>
+      <c r="K88" t="s">
+        <v>585</v>
+      </c>
+      <c r="L88" t="s">
         <v>588</v>
       </c>
-      <c r="G88" t="s">
-        <v>587</v>
-      </c>
-      <c r="H88" t="s">
-        <v>590</v>
-      </c>
-      <c r="I88" t="s">
-        <v>591</v>
-      </c>
-      <c r="J88" t="s">
-        <v>593</v>
-      </c>
-      <c r="K88" t="s">
-        <v>589</v>
-      </c>
-      <c r="L88" t="s">
-        <v>592</v>
-      </c>
       <c r="M88" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="N88" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="O88" s="11" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="P88" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="Q88" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="R88" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="89" spans="1:18">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" ht="16">
       <c r="A89" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B89" t="s">
+        <v>91</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="G89" t="s">
+        <v>333</v>
+      </c>
+      <c r="H89" t="s">
+        <v>232</v>
+      </c>
+      <c r="I89" t="s">
+        <v>91</v>
+      </c>
+      <c r="J89" t="s">
+        <v>92</v>
+      </c>
+      <c r="K89" t="s">
+        <v>91</v>
+      </c>
+      <c r="L89" t="s">
         <v>93</v>
       </c>
-      <c r="C89" s="9" t="s">
+      <c r="M89" t="s">
+        <v>94</v>
+      </c>
+      <c r="N89" t="s">
+        <v>642</v>
+      </c>
+      <c r="O89" s="11" t="s">
+        <v>695</v>
+      </c>
+      <c r="P89" t="s">
+        <v>91</v>
+      </c>
+      <c r="R89" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" ht="16">
+      <c r="A90" t="s">
+        <v>67</v>
+      </c>
+      <c r="B90" t="s">
+        <v>78</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="D90" s="9" t="s">
         <v>523</v>
       </c>
-      <c r="D89" s="9" t="s">
+      <c r="E90" s="9" t="s">
         <v>524</v>
       </c>
-      <c r="E89" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="G89" t="s">
-        <v>337</v>
-      </c>
-      <c r="H89" t="s">
-        <v>236</v>
-      </c>
-      <c r="I89" t="s">
-        <v>93</v>
-      </c>
-      <c r="J89" t="s">
-        <v>94</v>
-      </c>
-      <c r="K89" t="s">
-        <v>93</v>
-      </c>
-      <c r="L89" t="s">
-        <v>95</v>
-      </c>
-      <c r="M89" t="s">
-        <v>96</v>
-      </c>
-      <c r="N89" t="s">
-        <v>646</v>
-      </c>
-      <c r="O89" s="11" t="s">
-        <v>699</v>
-      </c>
-      <c r="P89" t="s">
-        <v>93</v>
-      </c>
-      <c r="R89" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="90" spans="1:18">
-      <c r="A90" t="s">
-        <v>69</v>
-      </c>
-      <c r="B90" t="s">
+      <c r="F90" t="s">
+        <v>364</v>
+      </c>
+      <c r="G90" t="s">
+        <v>320</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="I90" t="s">
+        <v>213</v>
+      </c>
+      <c r="J90" t="s">
+        <v>79</v>
+      </c>
+      <c r="K90" t="s">
         <v>80</v>
       </c>
-      <c r="C90" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="D90" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="E90" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="F90" t="s">
-        <v>368</v>
-      </c>
-      <c r="G90" t="s">
-        <v>324</v>
-      </c>
-      <c r="H90" s="9" t="s">
-        <v>576</v>
-      </c>
-      <c r="I90" t="s">
-        <v>217</v>
-      </c>
-      <c r="J90" t="s">
+      <c r="L90" t="s">
         <v>81</v>
       </c>
-      <c r="K90" t="s">
+      <c r="M90" t="s">
         <v>82</v>
       </c>
-      <c r="L90" t="s">
-        <v>83</v>
-      </c>
-      <c r="M90" t="s">
-        <v>84</v>
-      </c>
       <c r="N90" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="O90" s="12" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="P90" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="Q90" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="R90" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="91" spans="1:18">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" ht="16">
       <c r="A91" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B91" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="D91" s="9"/>
       <c r="F91" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="G91" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="I91" s="9" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="J91" s="9" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="K91" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="L91" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="M91" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="N91" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="O91" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="P91" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="Q91" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="R91" t="s">
-        <v>1018</v>
+        <v>999</v>
       </c>
     </row>
     <row r="92" spans="1:18">
       <c r="A92" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B92" t="s">
-        <v>889</v>
+        <v>882</v>
       </c>
       <c r="D92" s="9"/>
       <c r="G92"/>
       <c r="H92" s="9"/>
       <c r="I92" s="9"/>
       <c r="J92" s="9"/>
+      <c r="L92" t="s">
+        <v>1059</v>
+      </c>
       <c r="Q92" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
       <c r="R92" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="93" spans="1:18">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" ht="16">
       <c r="A93" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B93" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="G93"/>
       <c r="J93" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="L93" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="N93" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="O93" s="11" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="P93" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="Q93" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="R93" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="94" spans="1:18">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" ht="16">
       <c r="A94" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B94" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D94" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="G94"/>
       <c r="J94" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="L94" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="N94" t="s">
+        <v>645</v>
+      </c>
+      <c r="O94" s="11" t="s">
+        <v>698</v>
+      </c>
+      <c r="P94" t="s">
+        <v>809</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>866</v>
+      </c>
+      <c r="R94" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" ht="16">
+      <c r="A95" t="s">
+        <v>67</v>
+      </c>
+      <c r="B95" t="s">
+        <v>73</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="E95" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="G95" t="s">
+        <v>321</v>
+      </c>
+      <c r="H95" t="s">
+        <v>262</v>
+      </c>
+      <c r="I95" t="s">
+        <v>214</v>
+      </c>
+      <c r="J95" t="s">
+        <v>74</v>
+      </c>
+      <c r="K95" t="s">
+        <v>75</v>
+      </c>
+      <c r="L95" t="s">
+        <v>76</v>
+      </c>
+      <c r="M95" t="s">
+        <v>77</v>
+      </c>
+      <c r="N95" t="s">
+        <v>646</v>
+      </c>
+      <c r="O95" s="12" t="s">
+        <v>699</v>
+      </c>
+      <c r="P95" t="s">
+        <v>810</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>867</v>
+      </c>
+      <c r="R95" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" ht="16">
+      <c r="A96" t="s">
+        <v>67</v>
+      </c>
+      <c r="B96" t="s">
+        <v>576</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="G96" t="s">
+        <v>322</v>
+      </c>
+      <c r="H96" t="s">
+        <v>233</v>
+      </c>
+      <c r="I96" t="s">
+        <v>215</v>
+      </c>
+      <c r="J96" t="s">
+        <v>96</v>
+      </c>
+      <c r="K96" t="s">
+        <v>97</v>
+      </c>
+      <c r="L96" t="s">
+        <v>95</v>
+      </c>
+      <c r="M96" t="s">
+        <v>762</v>
+      </c>
+      <c r="N96" t="s">
+        <v>647</v>
+      </c>
+      <c r="O96" s="11" t="s">
+        <v>700</v>
+      </c>
+      <c r="P96" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>868</v>
+      </c>
+      <c r="R96" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" ht="16">
+      <c r="A97" t="s">
+        <v>165</v>
+      </c>
+      <c r="B97" t="s">
+        <v>898</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>899</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>900</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>901</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>902</v>
+      </c>
+      <c r="G97" t="s">
+        <v>903</v>
+      </c>
+      <c r="H97" t="s">
+        <v>904</v>
+      </c>
+      <c r="I97" t="s">
+        <v>905</v>
+      </c>
+      <c r="J97" t="s">
+        <v>906</v>
+      </c>
+      <c r="K97" t="s">
+        <v>907</v>
+      </c>
+      <c r="L97" t="s">
+        <v>898</v>
+      </c>
+      <c r="M97" t="s">
+        <v>166</v>
+      </c>
+      <c r="N97" t="s">
+        <v>648</v>
+      </c>
+      <c r="O97" s="11" t="s">
+        <v>701</v>
+      </c>
+      <c r="P97" t="s">
+        <v>811</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>869</v>
+      </c>
+      <c r="R97" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" ht="16">
+      <c r="A98" t="s">
+        <v>165</v>
+      </c>
+      <c r="B98" t="s">
+        <v>908</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>910</v>
+      </c>
+      <c r="E98" s="9" t="s">
+        <v>911</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>912</v>
+      </c>
+      <c r="G98" t="s">
+        <v>913</v>
+      </c>
+      <c r="H98" t="s">
+        <v>912</v>
+      </c>
+      <c r="I98" t="s">
+        <v>914</v>
+      </c>
+      <c r="J98" t="s">
+        <v>915</v>
+      </c>
+      <c r="K98" t="s">
+        <v>916</v>
+      </c>
+      <c r="L98" t="s">
+        <v>917</v>
+      </c>
+      <c r="M98" t="s">
+        <v>167</v>
+      </c>
+      <c r="N98" t="s">
         <v>649</v>
       </c>
-      <c r="O94" s="11" t="s">
+      <c r="O98" s="12" t="s">
         <v>702</v>
       </c>
-      <c r="P94" t="s">
-        <v>816</v>
-      </c>
-      <c r="Q94" t="s">
-        <v>873</v>
-      </c>
-      <c r="R94" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="95" spans="1:18">
-      <c r="A95" t="s">
-        <v>69</v>
-      </c>
-      <c r="B95" t="s">
-        <v>75</v>
-      </c>
-      <c r="C95" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="E95" s="9" t="s">
-        <v>536</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="G95" t="s">
-        <v>325</v>
-      </c>
-      <c r="H95" t="s">
-        <v>266</v>
-      </c>
-      <c r="I95" t="s">
-        <v>218</v>
-      </c>
-      <c r="J95" t="s">
-        <v>76</v>
-      </c>
-      <c r="K95" t="s">
-        <v>77</v>
-      </c>
-      <c r="L95" t="s">
-        <v>78</v>
-      </c>
-      <c r="M95" t="s">
-        <v>79</v>
-      </c>
-      <c r="N95" t="s">
-        <v>650</v>
-      </c>
-      <c r="O95" s="12" t="s">
-        <v>703</v>
-      </c>
-      <c r="P95" t="s">
-        <v>817</v>
-      </c>
-      <c r="Q95" t="s">
-        <v>874</v>
-      </c>
-      <c r="R95" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="96" spans="1:18">
-      <c r="A96" t="s">
-        <v>69</v>
-      </c>
-      <c r="B96" t="s">
-        <v>580</v>
-      </c>
-      <c r="C96" s="9" t="s">
-        <v>537</v>
-      </c>
-      <c r="D96" s="9" t="s">
-        <v>538</v>
-      </c>
-      <c r="E96" s="9" t="s">
-        <v>539</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="G96" t="s">
-        <v>326</v>
-      </c>
-      <c r="H96" t="s">
-        <v>237</v>
-      </c>
-      <c r="I96" t="s">
-        <v>219</v>
-      </c>
-      <c r="J96" t="s">
-        <v>98</v>
-      </c>
-      <c r="K96" t="s">
-        <v>99</v>
-      </c>
-      <c r="L96" t="s">
-        <v>97</v>
-      </c>
-      <c r="M96" t="s">
-        <v>769</v>
-      </c>
-      <c r="N96" t="s">
-        <v>651</v>
-      </c>
-      <c r="O96" s="11" t="s">
-        <v>704</v>
-      </c>
-      <c r="P96" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q96" t="s">
-        <v>875</v>
-      </c>
-      <c r="R96" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="97" spans="1:18">
-      <c r="A97" t="s">
-        <v>169</v>
-      </c>
-      <c r="B97" t="s">
-        <v>917</v>
-      </c>
-      <c r="C97" s="9" t="s">
-        <v>918</v>
-      </c>
-      <c r="D97" s="9" t="s">
-        <v>919</v>
-      </c>
-      <c r="E97" s="9" t="s">
-        <v>920</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>921</v>
-      </c>
-      <c r="G97" t="s">
-        <v>922</v>
-      </c>
-      <c r="H97" t="s">
-        <v>923</v>
-      </c>
-      <c r="I97" t="s">
-        <v>924</v>
-      </c>
-      <c r="J97" t="s">
-        <v>925</v>
-      </c>
-      <c r="K97" t="s">
-        <v>926</v>
-      </c>
-      <c r="L97" t="s">
-        <v>917</v>
-      </c>
-      <c r="M97" t="s">
-        <v>170</v>
-      </c>
-      <c r="N97" t="s">
-        <v>652</v>
-      </c>
-      <c r="O97" s="11" t="s">
-        <v>705</v>
-      </c>
-      <c r="P97" t="s">
-        <v>818</v>
-      </c>
-      <c r="Q97" t="s">
-        <v>876</v>
-      </c>
-      <c r="R97" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="98" spans="1:18">
-      <c r="A98" t="s">
-        <v>169</v>
-      </c>
-      <c r="B98" t="s">
-        <v>927</v>
-      </c>
-      <c r="C98" s="9" t="s">
-        <v>928</v>
-      </c>
-      <c r="D98" s="9" t="s">
-        <v>929</v>
-      </c>
-      <c r="E98" s="9" t="s">
-        <v>930</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>931</v>
-      </c>
-      <c r="G98" t="s">
-        <v>932</v>
-      </c>
-      <c r="H98" t="s">
-        <v>931</v>
-      </c>
-      <c r="I98" t="s">
-        <v>933</v>
-      </c>
-      <c r="J98" t="s">
-        <v>934</v>
-      </c>
-      <c r="K98" t="s">
-        <v>935</v>
-      </c>
-      <c r="L98" t="s">
-        <v>936</v>
-      </c>
-      <c r="M98" t="s">
-        <v>171</v>
-      </c>
-      <c r="N98" t="s">
-        <v>653</v>
-      </c>
-      <c r="O98" s="12" t="s">
-        <v>706</v>
-      </c>
       <c r="P98" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="Q98" t="s">
-        <v>877</v>
+        <v>870</v>
       </c>
       <c r="R98" t="s">
-        <v>1024</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="99" spans="1:18">
       <c r="A99" t="s">
-        <v>943</v>
+        <v>924</v>
       </c>
       <c r="B99" t="s">
-        <v>945</v>
+        <v>926</v>
       </c>
       <c r="D99" s="9"/>
       <c r="F99" t="s">
-        <v>948</v>
+        <v>929</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>947</v>
+        <v>928</v>
       </c>
       <c r="J99" t="s">
-        <v>950</v>
+        <v>931</v>
       </c>
       <c r="K99" t="s">
-        <v>952</v>
+        <v>933</v>
       </c>
       <c r="L99" t="s">
-        <v>954</v>
+        <v>935</v>
       </c>
       <c r="M99" t="s">
-        <v>956</v>
+        <v>937</v>
       </c>
       <c r="O99" s="12"/>
       <c r="R99" t="s">
-        <v>1025</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="100" spans="1:18">
       <c r="A100" t="s">
-        <v>943</v>
+        <v>924</v>
       </c>
       <c r="B100" t="s">
-        <v>944</v>
+        <v>925</v>
       </c>
       <c r="D100" s="9"/>
       <c r="F100" t="s">
-        <v>946</v>
+        <v>927</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>946</v>
+        <v>927</v>
       </c>
       <c r="J100" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="K100" t="s">
-        <v>951</v>
+        <v>932</v>
       </c>
       <c r="L100" t="s">
-        <v>953</v>
+        <v>934</v>
       </c>
       <c r="M100" t="s">
-        <v>955</v>
+        <v>936</v>
       </c>
       <c r="O100" s="12"/>
       <c r="R100" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" ht="32">
+      <c r="A101" t="s">
+        <v>608</v>
+      </c>
+      <c r="B101" t="s">
+        <v>171</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="G101" t="s">
+        <v>323</v>
+      </c>
+      <c r="J101" t="s">
+        <v>273</v>
+      </c>
+      <c r="L101" t="s">
+        <v>730</v>
+      </c>
+      <c r="O101" s="11" t="s">
+        <v>703</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>871</v>
+      </c>
+      <c r="R101" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="28.5">
-      <c r="A101" t="s">
-        <v>612</v>
-      </c>
-      <c r="B101" t="s">
-        <v>175</v>
-      </c>
-      <c r="C101" s="9" t="s">
+    <row r="102" spans="1:18" ht="32">
+      <c r="A102" t="s">
+        <v>608</v>
+      </c>
+      <c r="B102" t="s">
+        <v>169</v>
+      </c>
+      <c r="C102" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="D102" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="D101" s="9" t="s">
+      <c r="E102" s="9" t="s">
         <v>541</v>
       </c>
-      <c r="E101" s="9" t="s">
+      <c r="F102" t="s">
+        <v>368</v>
+      </c>
+      <c r="G102" t="s">
+        <v>324</v>
+      </c>
+      <c r="J102" t="s">
+        <v>274</v>
+      </c>
+      <c r="L102" t="s">
+        <v>1060</v>
+      </c>
+      <c r="O102" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>872</v>
+      </c>
+      <c r="R102" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" ht="32">
+      <c r="A103" t="s">
+        <v>608</v>
+      </c>
+      <c r="B103" t="s">
+        <v>168</v>
+      </c>
+      <c r="C103" s="9" t="s">
         <v>542</v>
       </c>
-      <c r="F101" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="G101" t="s">
-        <v>327</v>
-      </c>
-      <c r="J101" t="s">
-        <v>277</v>
-      </c>
-      <c r="L101" t="s">
-        <v>735</v>
-      </c>
-      <c r="O101" s="11" t="s">
-        <v>707</v>
-      </c>
-      <c r="Q101" s="14" t="s">
-        <v>878</v>
-      </c>
-      <c r="R101" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="102" spans="1:18" ht="28.5">
-      <c r="A102" t="s">
-        <v>612</v>
-      </c>
-      <c r="B102" t="s">
-        <v>173</v>
-      </c>
-      <c r="C102" s="9" t="s">
+      <c r="D103" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D102" s="9" t="s">
+      <c r="E103" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="E102" s="9" t="s">
-        <v>545</v>
-      </c>
-      <c r="F102" t="s">
-        <v>372</v>
-      </c>
-      <c r="G102" t="s">
-        <v>328</v>
-      </c>
-      <c r="J102" t="s">
-        <v>278</v>
-      </c>
-      <c r="L102" t="s">
-        <v>736</v>
-      </c>
-      <c r="O102" s="11" t="s">
-        <v>708</v>
-      </c>
-      <c r="Q102" s="14" t="s">
-        <v>879</v>
-      </c>
-      <c r="R102" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="103" spans="1:18" ht="28.5">
-      <c r="A103" t="s">
-        <v>612</v>
-      </c>
-      <c r="B103" t="s">
-        <v>172</v>
-      </c>
-      <c r="C103" s="9" t="s">
-        <v>546</v>
-      </c>
-      <c r="D103" s="9" t="s">
-        <v>547</v>
-      </c>
-      <c r="E103" s="9" t="s">
-        <v>548</v>
-      </c>
       <c r="F103" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="G103"/>
       <c r="J103" t="s">
+        <v>275</v>
+      </c>
+      <c r="L103" t="s">
+        <v>1061</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>873</v>
+      </c>
+      <c r="R103" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" ht="16">
+      <c r="A104" t="s">
+        <v>608</v>
+      </c>
+      <c r="B104" t="s">
+        <v>176</v>
+      </c>
+      <c r="C104" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="E104" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="F104" t="s">
+        <v>370</v>
+      </c>
+      <c r="G104" t="s">
+        <v>325</v>
+      </c>
+      <c r="J104" t="s">
+        <v>276</v>
+      </c>
+      <c r="L104" t="s">
+        <v>731</v>
+      </c>
+      <c r="O104" s="12" t="s">
+        <v>705</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>874</v>
+      </c>
+      <c r="R104" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" ht="16">
+      <c r="A105" t="s">
+        <v>608</v>
+      </c>
+      <c r="B105" t="s">
+        <v>178</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="E105" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="F105" t="s">
+        <v>371</v>
+      </c>
+      <c r="G105" t="s">
+        <v>326</v>
+      </c>
+      <c r="J105" t="s">
+        <v>277</v>
+      </c>
+      <c r="L105" t="s">
+        <v>732</v>
+      </c>
+      <c r="O105" s="12" t="s">
+        <v>706</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>875</v>
+      </c>
+      <c r="R105" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" ht="48">
+      <c r="A106" t="s">
+        <v>608</v>
+      </c>
+      <c r="B106" t="s">
+        <v>173</v>
+      </c>
+      <c r="C106" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="E106" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="F106" t="s">
+        <v>372</v>
+      </c>
+      <c r="G106" t="s">
+        <v>327</v>
+      </c>
+      <c r="J106" t="s">
+        <v>278</v>
+      </c>
+      <c r="L106" t="s">
+        <v>733</v>
+      </c>
+      <c r="O106" s="12" t="s">
+        <v>707</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>876</v>
+      </c>
+      <c r="R106" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" ht="32">
+      <c r="A107" t="s">
+        <v>608</v>
+      </c>
+      <c r="B107" t="s">
+        <v>172</v>
+      </c>
+      <c r="C107" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="E107" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="F107" t="s">
+        <v>373</v>
+      </c>
+      <c r="G107" t="s">
+        <v>328</v>
+      </c>
+      <c r="J107" t="s">
         <v>279</v>
       </c>
-      <c r="L103" t="s">
+      <c r="L107" t="s">
+        <v>734</v>
+      </c>
+      <c r="O107" s="12" t="s">
+        <v>708</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>877</v>
+      </c>
+      <c r="R107" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" ht="32">
+      <c r="A108" t="s">
+        <v>608</v>
+      </c>
+      <c r="B108" t="s">
+        <v>174</v>
+      </c>
+      <c r="C108" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="E108" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="F108" t="s">
+        <v>374</v>
+      </c>
+      <c r="G108" t="s">
+        <v>329</v>
+      </c>
+      <c r="J108" t="s">
+        <v>280</v>
+      </c>
+      <c r="L108" t="s">
+        <v>735</v>
+      </c>
+      <c r="O108" s="12" t="s">
+        <v>709</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>878</v>
+      </c>
+      <c r="R108" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" ht="32">
+      <c r="A109" t="s">
+        <v>608</v>
+      </c>
+      <c r="B109" t="s">
+        <v>177</v>
+      </c>
+      <c r="C109" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="E109" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="J109" t="s">
+        <v>281</v>
+      </c>
+      <c r="L109" t="s">
+        <v>738</v>
+      </c>
+      <c r="O109" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>879</v>
+      </c>
+      <c r="R109" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" ht="16">
+      <c r="A110" t="s">
+        <v>608</v>
+      </c>
+      <c r="B110" t="s">
+        <v>170</v>
+      </c>
+      <c r="C110" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="E110" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="F110" t="s">
+        <v>376</v>
+      </c>
+      <c r="G110" t="s">
+        <v>331</v>
+      </c>
+      <c r="J110" t="s">
+        <v>282</v>
+      </c>
+      <c r="L110" t="s">
+        <v>736</v>
+      </c>
+      <c r="O110" s="12" t="s">
+        <v>711</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>880</v>
+      </c>
+      <c r="R110" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" ht="16">
+      <c r="A111" t="s">
+        <v>608</v>
+      </c>
+      <c r="B111" t="s">
+        <v>175</v>
+      </c>
+      <c r="C111" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="E111" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="F111" t="s">
+        <v>377</v>
+      </c>
+      <c r="G111" t="s">
+        <v>332</v>
+      </c>
+      <c r="J111" t="s">
+        <v>283</v>
+      </c>
+      <c r="L111" t="s">
         <v>737</v>
       </c>
-      <c r="Q103" s="14" t="s">
-        <v>880</v>
-      </c>
-      <c r="R103" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="104" spans="1:18">
-      <c r="A104" t="s">
-        <v>612</v>
-      </c>
-      <c r="B104" t="s">
-        <v>180</v>
-      </c>
-      <c r="C104" s="9" t="s">
-        <v>549</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>550</v>
-      </c>
-      <c r="E104" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="F104" t="s">
-        <v>374</v>
-      </c>
-      <c r="G104" t="s">
-        <v>329</v>
-      </c>
-      <c r="J104" t="s">
-        <v>280</v>
-      </c>
-      <c r="L104" t="s">
-        <v>738</v>
-      </c>
-      <c r="O104" s="12" t="s">
-        <v>709</v>
-      </c>
-      <c r="Q104" s="14" t="s">
+      <c r="O111" s="12" t="s">
+        <v>712</v>
+      </c>
+      <c r="Q111" t="s">
         <v>881</v>
       </c>
-      <c r="R104" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="105" spans="1:18">
-      <c r="A105" t="s">
-        <v>612</v>
-      </c>
-      <c r="B105" t="s">
-        <v>182</v>
-      </c>
-      <c r="C105" s="9" t="s">
-        <v>552</v>
-      </c>
-      <c r="D105" s="9" t="s">
-        <v>553</v>
-      </c>
-      <c r="E105" s="9" t="s">
-        <v>554</v>
-      </c>
-      <c r="F105" t="s">
-        <v>375</v>
-      </c>
-      <c r="G105" t="s">
-        <v>330</v>
-      </c>
-      <c r="J105" t="s">
-        <v>281</v>
-      </c>
-      <c r="L105" t="s">
-        <v>739</v>
-      </c>
-      <c r="O105" s="12" t="s">
-        <v>710</v>
-      </c>
-      <c r="Q105" s="14" t="s">
-        <v>882</v>
-      </c>
-      <c r="R105" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="106" spans="1:18" ht="28.5">
-      <c r="A106" t="s">
-        <v>612</v>
-      </c>
-      <c r="B106" t="s">
-        <v>177</v>
-      </c>
-      <c r="C106" s="9" t="s">
-        <v>555</v>
-      </c>
-      <c r="D106" s="9" t="s">
-        <v>556</v>
-      </c>
-      <c r="E106" s="9" t="s">
-        <v>557</v>
-      </c>
-      <c r="F106" t="s">
-        <v>376</v>
-      </c>
-      <c r="G106" t="s">
-        <v>331</v>
-      </c>
-      <c r="J106" t="s">
-        <v>282</v>
-      </c>
-      <c r="L106" t="s">
-        <v>740</v>
-      </c>
-      <c r="O106" s="12" t="s">
-        <v>711</v>
-      </c>
-      <c r="Q106" s="14" t="s">
-        <v>883</v>
-      </c>
-      <c r="R106" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="107" spans="1:18" ht="28.5">
-      <c r="A107" t="s">
-        <v>612</v>
-      </c>
-      <c r="B107" t="s">
-        <v>176</v>
-      </c>
-      <c r="C107" s="9" t="s">
-        <v>558</v>
-      </c>
-      <c r="D107" s="9" t="s">
-        <v>559</v>
-      </c>
-      <c r="E107" s="9" t="s">
-        <v>560</v>
-      </c>
-      <c r="F107" t="s">
-        <v>377</v>
-      </c>
-      <c r="G107" t="s">
-        <v>332</v>
-      </c>
-      <c r="J107" t="s">
-        <v>283</v>
-      </c>
-      <c r="L107" t="s">
-        <v>741</v>
-      </c>
-      <c r="O107" s="12" t="s">
-        <v>712</v>
-      </c>
-      <c r="Q107" s="14" t="s">
-        <v>884</v>
-      </c>
-      <c r="R107" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="108" spans="1:18" ht="28.5">
-      <c r="A108" t="s">
-        <v>612</v>
-      </c>
-      <c r="B108" t="s">
-        <v>178</v>
-      </c>
-      <c r="C108" s="9" t="s">
-        <v>561</v>
-      </c>
-      <c r="D108" s="9" t="s">
-        <v>562</v>
-      </c>
-      <c r="E108" s="9" t="s">
-        <v>563</v>
-      </c>
-      <c r="F108" t="s">
-        <v>378</v>
-      </c>
-      <c r="G108" t="s">
-        <v>333</v>
-      </c>
-      <c r="J108" t="s">
-        <v>284</v>
-      </c>
-      <c r="L108" t="s">
-        <v>742</v>
-      </c>
-      <c r="O108" s="12" t="s">
-        <v>713</v>
-      </c>
-      <c r="Q108" s="14" t="s">
-        <v>885</v>
-      </c>
-      <c r="R108" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="109" spans="1:18" ht="28.5">
-      <c r="A109" t="s">
-        <v>612</v>
-      </c>
-      <c r="B109" t="s">
-        <v>181</v>
-      </c>
-      <c r="C109" s="9" t="s">
-        <v>564</v>
-      </c>
-      <c r="D109" s="9" t="s">
-        <v>565</v>
-      </c>
-      <c r="E109" s="9" t="s">
-        <v>566</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="J109" t="s">
-        <v>285</v>
-      </c>
-      <c r="L109" t="s">
-        <v>745</v>
-      </c>
-      <c r="O109" s="12" t="s">
-        <v>714</v>
-      </c>
-      <c r="Q109" s="14" t="s">
-        <v>886</v>
-      </c>
-      <c r="R109" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="110" spans="1:18">
-      <c r="A110" t="s">
-        <v>612</v>
-      </c>
-      <c r="B110" t="s">
-        <v>174</v>
-      </c>
-      <c r="C110" s="9" t="s">
-        <v>567</v>
-      </c>
-      <c r="D110" s="9" t="s">
-        <v>568</v>
-      </c>
-      <c r="E110" s="9" t="s">
-        <v>569</v>
-      </c>
-      <c r="F110" t="s">
-        <v>380</v>
-      </c>
-      <c r="G110" t="s">
-        <v>335</v>
-      </c>
-      <c r="J110" t="s">
-        <v>286</v>
-      </c>
-      <c r="L110" t="s">
-        <v>743</v>
-      </c>
-      <c r="O110" s="12" t="s">
-        <v>715</v>
-      </c>
-      <c r="Q110" s="14" t="s">
-        <v>887</v>
-      </c>
-      <c r="R110" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="111" spans="1:18">
-      <c r="A111" t="s">
-        <v>612</v>
-      </c>
-      <c r="B111" t="s">
-        <v>179</v>
-      </c>
-      <c r="C111" s="9" t="s">
-        <v>570</v>
-      </c>
-      <c r="D111" s="9" t="s">
-        <v>571</v>
-      </c>
-      <c r="E111" s="9" t="s">
-        <v>572</v>
-      </c>
-      <c r="F111" t="s">
-        <v>381</v>
-      </c>
-      <c r="G111" t="s">
-        <v>336</v>
-      </c>
-      <c r="J111" t="s">
-        <v>287</v>
-      </c>
-      <c r="L111" t="s">
-        <v>744</v>
-      </c>
-      <c r="O111" s="12" t="s">
-        <v>716</v>
-      </c>
-      <c r="Q111" s="14" t="s">
-        <v>888</v>
-      </c>
       <c r="R111" t="s">
-        <v>1051</v>
+        <v>1032</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/gtsummary_translated.xlsx
+++ b/data-raw/gtsummary_translated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sjobergd/Documents/GitHub/gtsummary/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7BC3EB0-4D26-CA43-B0CD-29E421BECF0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3B4C68-BEF1-8642-A807-50379B447F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10180" yWindow="22360" windowWidth="30240" windowHeight="18880" xr2:uid="{24D5C74B-D2E9-42BC-9756-BFD64AB81539}"/>
   </bookViews>
@@ -3300,9 +3300,6 @@
     <t>Contrastes marginaux à la moyenne</t>
   </si>
   <si>
-    <t xml:space="preserve"> Contrastes marginaux aux moyennes marginales</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Contrastes marginaux</t>
   </si>
   <si>
@@ -3325,6 +3322,9 @@
   </si>
   <si>
     <t>test du khi-deux avec la correction du second ordre de Rao &amp; Scott</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Prédictions marginales aux moyennes marginales</t>
   </si>
 </sst>
 </file>
@@ -6069,7 +6069,7 @@
       <c r="E65"/>
       <c r="G65"/>
       <c r="L65" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="R65" t="s">
         <v>980</v>
@@ -6086,7 +6086,7 @@
       <c r="E66"/>
       <c r="G66"/>
       <c r="L66" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="R66" t="s">
         <v>981</v>
@@ -6103,7 +6103,7 @@
       <c r="E67"/>
       <c r="G67"/>
       <c r="L67" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="R67" t="s">
         <v>982</v>
@@ -6120,7 +6120,7 @@
       <c r="E68"/>
       <c r="G68"/>
       <c r="L68" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="R68" t="s">
         <v>983</v>
@@ -6137,7 +6137,7 @@
       <c r="E69"/>
       <c r="G69"/>
       <c r="L69" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="R69" t="s">
         <v>984</v>
@@ -6154,7 +6154,7 @@
       <c r="E70"/>
       <c r="G70"/>
       <c r="L70" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="R70" t="s">
         <v>985</v>
@@ -7204,7 +7204,7 @@
       <c r="I92" s="9"/>
       <c r="J92" s="9"/>
       <c r="L92" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="Q92" t="s">
         <v>883</v>
@@ -7641,7 +7641,7 @@
         <v>274</v>
       </c>
       <c r="L102" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="O102" s="11" t="s">
         <v>704</v>
@@ -7677,7 +7677,7 @@
         <v>275</v>
       </c>
       <c r="L103" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="Q103" t="s">
         <v>873</v>
